--- a/Shablon/Г7М-20А-6.xlsx
+++ b/Shablon/Г7М-20А-6.xlsx
@@ -19,10 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="220">
-  <si>
-    <t>СГМетр, лаборатория средств электрорадиотехнических измерений</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="215">
   <si>
     <t>MY54490652</t>
   </si>
@@ -85,18 +82,6 @@
       </rPr>
       <t>, МГц</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">АО "Гос МКБ "Вымпел" им. И.И. Торопова. </t>
-  </si>
-  <si>
-    <t>Уникальный номер об аккредитации в реестре аккредитованных лиц № РОСС СОБ 3.00231.2014</t>
-  </si>
-  <si>
-    <t>125424, г. Москва, Волоколамское шоссе, дом 90, стр. 23</t>
-  </si>
-  <si>
-    <t>Тел.+7(495)491-05-31, 22-68, факс +7(495)490-22-22, e-mail: ogmetr@vympelmkb.com</t>
   </si>
   <si>
     <t>периодическая</t>
@@ -1139,93 +1124,72 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1276,29 +1240,50 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1589,83 +1574,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
+      <c r="A1" s="67"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
+      <c r="A2" s="67"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="71" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
+      <c r="A3" s="67"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="71" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="71"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="71"/>
-      <c r="I4" s="71"/>
+      <c r="A4" s="67"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="72" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
+      <c r="A5" s="68"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="75" t="str">
+      <c r="A7" s="70" t="str">
         <f>"Протокол поверки № 10/"&amp;C198&amp;"/"&amp;D10</f>
         <v>Протокол поверки № 10/_date/_numb</v>
       </c>
-      <c r="B7" s="75"/>
-      <c r="C7" s="75"/>
-      <c r="D7" s="75"/>
-      <c r="E7" s="75"/>
-      <c r="F7" s="75"/>
-      <c r="G7" s="75"/>
-      <c r="H7" s="75"/>
-      <c r="I7" s="75"/>
+      <c r="B7" s="70"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="70"/>
+      <c r="G7" s="70"/>
+      <c r="H7" s="70"/>
+      <c r="I7" s="70"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="18"/>
@@ -1679,30 +1654,30 @@
       <c r="I8" s="19"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="73" t="s">
-        <v>70</v>
-      </c>
-      <c r="B9" s="73"/>
-      <c r="C9" s="74"/>
+      <c r="A9" s="62" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="62"/>
+      <c r="C9" s="69"/>
       <c r="D9" s="40" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E9" s="35"/>
       <c r="F9" s="36" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G9" s="35"/>
       <c r="H9" s="37"/>
       <c r="I9" s="19"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="73" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="73"/>
-      <c r="C10" s="74"/>
+      <c r="A10" s="62" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="62"/>
+      <c r="C10" s="69"/>
       <c r="D10" s="38" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E10" s="34"/>
       <c r="F10" s="34"/>
@@ -1711,43 +1686,43 @@
       <c r="I10" s="19"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="79" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="79"/>
-      <c r="C11" s="79"/>
-      <c r="D11" s="80">
+      <c r="A11" s="72" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="72"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="73">
         <v>44043</v>
       </c>
-      <c r="E11" s="81"/>
-      <c r="F11" s="81"/>
-      <c r="G11" s="81"/>
-      <c r="H11" s="81"/>
+      <c r="E11" s="74"/>
+      <c r="F11" s="74"/>
+      <c r="G11" s="74"/>
+      <c r="H11" s="74"/>
       <c r="I11" s="19"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="79" t="s">
-        <v>72</v>
-      </c>
-      <c r="B12" s="79"/>
-      <c r="C12" s="79"/>
-      <c r="D12" s="82" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" s="82"/>
-      <c r="F12" s="82"/>
-      <c r="G12" s="82"/>
-      <c r="H12" s="82"/>
+      <c r="A12" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" s="72"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="75" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="75"/>
+      <c r="F12" s="75"/>
+      <c r="G12" s="75"/>
+      <c r="H12" s="75"/>
       <c r="I12" s="19"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="73" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" s="73"/>
-      <c r="C13" s="74"/>
+      <c r="A13" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="62"/>
+      <c r="C13" s="69"/>
       <c r="D13" s="38" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E13" s="34"/>
       <c r="F13" s="34"/>
@@ -1756,63 +1731,63 @@
       <c r="I13" s="19"/>
     </row>
     <row r="14" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="69" t="s">
-        <v>74</v>
-      </c>
-      <c r="B14" s="69"/>
-      <c r="C14" s="69"/>
-      <c r="D14" s="93" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="93"/>
-      <c r="F14" s="93"/>
-      <c r="G14" s="93"/>
-      <c r="H14" s="93"/>
+      <c r="A14" s="60" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" s="60"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="61" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="61"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="61"/>
       <c r="I14" s="19"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="73" t="s">
-        <v>75</v>
-      </c>
-      <c r="B15" s="73"/>
-      <c r="C15" s="73"/>
-      <c r="D15" s="77" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="77"/>
-      <c r="F15" s="77"/>
-      <c r="G15" s="77"/>
-      <c r="H15" s="77"/>
+      <c r="A15" s="62" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="62"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="63" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="63"/>
+      <c r="F15" s="63"/>
+      <c r="G15" s="63"/>
+      <c r="H15" s="63"/>
       <c r="I15" s="19"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="73" t="s">
-        <v>76</v>
-      </c>
-      <c r="B16" s="73"/>
-      <c r="C16" s="73"/>
-      <c r="D16" s="77" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="77"/>
-      <c r="F16" s="77"/>
-      <c r="G16" s="77"/>
-      <c r="H16" s="77"/>
+      <c r="A16" s="62" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="62"/>
+      <c r="C16" s="62"/>
+      <c r="D16" s="63" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="63"/>
+      <c r="F16" s="63"/>
+      <c r="G16" s="63"/>
+      <c r="H16" s="63"/>
       <c r="I16" s="19"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="B17" s="73"/>
-      <c r="C17" s="73"/>
-      <c r="D17" s="77" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="77"/>
-      <c r="F17" s="77"/>
-      <c r="G17" s="77"/>
-      <c r="H17" s="77"/>
+      <c r="A17" s="62" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="62"/>
+      <c r="C17" s="62"/>
+      <c r="D17" s="63" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="63"/>
+      <c r="F17" s="63"/>
+      <c r="G17" s="63"/>
+      <c r="H17" s="63"/>
       <c r="I17" s="19"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -1827,12 +1802,12 @@
       <c r="I18" s="19"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="78" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="78"/>
-      <c r="C19" s="78"/>
-      <c r="D19" s="78"/>
+      <c r="A19" s="71" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="71"/>
+      <c r="C19" s="71"/>
+      <c r="D19" s="71"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
       <c r="G19" s="9"/>
@@ -1840,82 +1815,82 @@
       <c r="I19" s="19"/>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="87" t="s">
+      <c r="A20" s="80" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20" s="81"/>
+      <c r="C20" s="81"/>
+      <c r="D20" s="82"/>
+      <c r="E20" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="88"/>
-      <c r="C20" s="88"/>
-      <c r="D20" s="89"/>
-      <c r="E20" s="83" t="s">
+      <c r="F20" s="77"/>
+      <c r="G20" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="F20" s="84"/>
-      <c r="G20" s="83" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="84"/>
+      <c r="H20" s="77"/>
       <c r="I20" s="19"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="90"/>
-      <c r="B21" s="91"/>
-      <c r="C21" s="91"/>
-      <c r="D21" s="92"/>
-      <c r="E21" s="85"/>
-      <c r="F21" s="86"/>
-      <c r="G21" s="85"/>
-      <c r="H21" s="86"/>
+      <c r="A21" s="83"/>
+      <c r="B21" s="84"/>
+      <c r="C21" s="84"/>
+      <c r="D21" s="85"/>
+      <c r="E21" s="78"/>
+      <c r="F21" s="79"/>
+      <c r="G21" s="78"/>
+      <c r="H21" s="79"/>
       <c r="I21" s="19"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="21" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B22" s="21"/>
       <c r="C22" s="21"/>
       <c r="D22" s="21"/>
-      <c r="E22" s="76" t="s">
-        <v>82</v>
-      </c>
-      <c r="F22" s="76"/>
-      <c r="G22" s="70" t="s">
-        <v>22</v>
-      </c>
-      <c r="H22" s="70"/>
+      <c r="E22" s="64" t="s">
+        <v>77</v>
+      </c>
+      <c r="F22" s="64"/>
+      <c r="G22" s="65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="65"/>
       <c r="I22" s="19"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="73" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="73"/>
-      <c r="C23" s="73"/>
-      <c r="D23" s="73"/>
-      <c r="E23" s="76" t="s">
-        <v>83</v>
-      </c>
-      <c r="F23" s="76"/>
-      <c r="G23" s="70" t="s">
-        <v>24</v>
-      </c>
-      <c r="H23" s="70"/>
+      <c r="A23" s="62" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" s="62"/>
+      <c r="C23" s="62"/>
+      <c r="D23" s="62"/>
+      <c r="E23" s="64" t="s">
+        <v>78</v>
+      </c>
+      <c r="F23" s="64"/>
+      <c r="G23" s="65" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" s="65"/>
       <c r="I23" s="19"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="73" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="73"/>
-      <c r="C24" s="73"/>
-      <c r="D24" s="73"/>
-      <c r="E24" s="76" t="s">
-        <v>84</v>
-      </c>
-      <c r="F24" s="76"/>
-      <c r="G24" s="70" t="s">
-        <v>26</v>
-      </c>
-      <c r="H24" s="70"/>
+      <c r="A24" s="62" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="62"/>
+      <c r="C24" s="62"/>
+      <c r="D24" s="62"/>
+      <c r="E24" s="64" t="s">
+        <v>79</v>
+      </c>
+      <c r="F24" s="64"/>
+      <c r="G24" s="65" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" s="65"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="20"/>
@@ -1930,7 +1905,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="22" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B26" s="22"/>
       <c r="C26" s="22"/>
@@ -1942,89 +1917,89 @@
       <c r="I26" s="23"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="94" t="s">
+      <c r="A27" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27" s="66"/>
+      <c r="C27" s="66"/>
+      <c r="D27" s="66"/>
+      <c r="E27" s="66" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" s="66"/>
+      <c r="G27" s="66" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="66"/>
+      <c r="I27" s="66"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="60"/>
+      <c r="C28" s="60"/>
+      <c r="D28" s="60"/>
+      <c r="E28" s="65">
+        <v>1601</v>
+      </c>
+      <c r="F28" s="65"/>
+      <c r="G28" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="H28" s="49"/>
+      <c r="I28" s="49"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="60" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="60"/>
+      <c r="C29" s="60"/>
+      <c r="D29" s="60"/>
+      <c r="E29" s="65">
+        <v>418840</v>
+      </c>
+      <c r="F29" s="65"/>
+      <c r="G29" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="H29" s="49"/>
+      <c r="I29" s="49"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="94"/>
-      <c r="C27" s="94"/>
-      <c r="D27" s="94"/>
-      <c r="E27" s="94" t="s">
-        <v>30</v>
-      </c>
-      <c r="F27" s="94"/>
-      <c r="G27" s="94" t="s">
-        <v>31</v>
-      </c>
-      <c r="H27" s="94"/>
-      <c r="I27" s="94"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="69" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" s="69"/>
-      <c r="C28" s="69"/>
-      <c r="D28" s="69"/>
-      <c r="E28" s="70">
-        <v>1601</v>
-      </c>
-      <c r="F28" s="70"/>
-      <c r="G28" s="54" t="s">
-        <v>67</v>
-      </c>
-      <c r="H28" s="54"/>
-      <c r="I28" s="54"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="69" t="s">
-        <v>33</v>
-      </c>
-      <c r="B29" s="69"/>
-      <c r="C29" s="69"/>
-      <c r="D29" s="69"/>
-      <c r="E29" s="70">
-        <v>418840</v>
-      </c>
-      <c r="F29" s="70"/>
-      <c r="G29" s="54" t="s">
-        <v>68</v>
-      </c>
-      <c r="H29" s="54"/>
-      <c r="I29" s="54"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="69" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="69"/>
-      <c r="C30" s="69"/>
-      <c r="D30" s="69"/>
-      <c r="E30" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="F30" s="70"/>
-      <c r="G30" s="54" t="s">
-        <v>69</v>
-      </c>
-      <c r="H30" s="54"/>
-      <c r="I30" s="54"/>
+      <c r="B30" s="60"/>
+      <c r="C30" s="60"/>
+      <c r="D30" s="60"/>
+      <c r="E30" s="65" t="s">
+        <v>0</v>
+      </c>
+      <c r="F30" s="65"/>
+      <c r="G30" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="H30" s="49"/>
+      <c r="I30" s="49"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="69" t="s">
-        <v>65</v>
-      </c>
-      <c r="B31" s="69"/>
-      <c r="C31" s="69"/>
-      <c r="D31" s="69"/>
-      <c r="E31" s="70">
+      <c r="A31" s="60" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="60"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="60"/>
+      <c r="E31" s="65">
         <v>101324</v>
       </c>
-      <c r="F31" s="70"/>
-      <c r="G31" s="54" t="s">
-        <v>66</v>
-      </c>
-      <c r="H31" s="54"/>
-      <c r="I31" s="54"/>
+      <c r="F31" s="65"/>
+      <c r="G31" s="49" t="s">
+        <v>61</v>
+      </c>
+      <c r="H31" s="49"/>
+      <c r="I31" s="49"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="22"/>
@@ -2039,7 +2014,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -2051,7 +2026,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -2063,7 +2038,7 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -2086,21 +2061,21 @@
       <c r="I36" s="17"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="99" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="100"/>
-      <c r="C37" s="100"/>
-      <c r="D37" s="100"/>
-      <c r="E37" s="100"/>
-      <c r="F37" s="100"/>
-      <c r="G37" s="100"/>
-      <c r="H37" s="100"/>
-      <c r="I37" s="100"/>
+      <c r="A37" s="87" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="88"/>
+      <c r="C37" s="88"/>
+      <c r="D37" s="88"/>
+      <c r="E37" s="88"/>
+      <c r="F37" s="88"/>
+      <c r="G37" s="88"/>
+      <c r="H37" s="88"/>
+      <c r="I37" s="88"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B38" s="24"/>
       <c r="C38" s="24"/>
@@ -2112,22 +2087,22 @@
       <c r="I38" s="24"/>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="61" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="62"/>
-      <c r="C39" s="61" t="s">
-        <v>63</v>
-      </c>
-      <c r="D39" s="62"/>
-      <c r="E39" s="61" t="s">
-        <v>138</v>
-      </c>
-      <c r="F39" s="62"/>
-      <c r="G39" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="H39" s="62"/>
+      <c r="A39" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39" s="57"/>
+      <c r="C39" s="56" t="s">
+        <v>58</v>
+      </c>
+      <c r="D39" s="57"/>
+      <c r="E39" s="56" t="s">
+        <v>133</v>
+      </c>
+      <c r="F39" s="57"/>
+      <c r="G39" s="58" t="s">
+        <v>132</v>
+      </c>
+      <c r="H39" s="57"/>
       <c r="I39" s="24"/>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -2135,17 +2110,17 @@
         <v>10</v>
       </c>
       <c r="B40" s="59"/>
-      <c r="C40" s="58" t="s">
-        <v>91</v>
-      </c>
-      <c r="D40" s="58"/>
+      <c r="C40" s="86" t="s">
+        <v>86</v>
+      </c>
+      <c r="D40" s="86"/>
       <c r="E40" s="59" t="e">
         <f>(C40-A40*1000000)/A40</f>
         <v>#VALUE!</v>
       </c>
       <c r="F40" s="59"/>
       <c r="G40" s="59" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H40" s="59"/>
       <c r="I40" s="24"/>
@@ -2162,46 +2137,46 @@
       <c r="I41" s="24"/>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="56" t="s">
-        <v>46</v>
-      </c>
-      <c r="B42" s="56"/>
-      <c r="C42" s="56"/>
-      <c r="D42" s="56"/>
-      <c r="E42" s="56"/>
-      <c r="F42" s="56"/>
-      <c r="G42" s="56"/>
-      <c r="H42" s="56"/>
-      <c r="I42" s="56"/>
+      <c r="A42" s="96" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="96"/>
+      <c r="C42" s="96"/>
+      <c r="D42" s="96"/>
+      <c r="E42" s="96"/>
+      <c r="F42" s="96"/>
+      <c r="G42" s="96"/>
+      <c r="H42" s="96"/>
+      <c r="I42" s="96"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="56"/>
-      <c r="B43" s="56"/>
-      <c r="C43" s="56"/>
-      <c r="D43" s="56"/>
-      <c r="E43" s="56"/>
-      <c r="F43" s="56"/>
-      <c r="G43" s="56"/>
-      <c r="H43" s="56"/>
-      <c r="I43" s="56"/>
+      <c r="A43" s="96"/>
+      <c r="B43" s="96"/>
+      <c r="C43" s="96"/>
+      <c r="D43" s="96"/>
+      <c r="E43" s="96"/>
+      <c r="F43" s="96"/>
+      <c r="G43" s="96"/>
+      <c r="H43" s="96"/>
+      <c r="I43" s="96"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="61" t="s">
-        <v>13</v>
-      </c>
-      <c r="B44" s="62"/>
-      <c r="C44" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="D44" s="62"/>
-      <c r="E44" s="61" t="s">
-        <v>138</v>
-      </c>
-      <c r="F44" s="62"/>
-      <c r="G44" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="H44" s="62"/>
+      <c r="A44" s="56" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" s="57"/>
+      <c r="C44" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="D44" s="57"/>
+      <c r="E44" s="56" t="s">
+        <v>133</v>
+      </c>
+      <c r="F44" s="57"/>
+      <c r="G44" s="58" t="s">
+        <v>132</v>
+      </c>
+      <c r="H44" s="57"/>
       <c r="I44" s="24"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
@@ -2209,19 +2184,19 @@
         <v>10</v>
       </c>
       <c r="B45" s="59"/>
-      <c r="C45" s="58" t="s">
-        <v>92</v>
-      </c>
-      <c r="D45" s="58"/>
+      <c r="C45" s="86" t="s">
+        <v>87</v>
+      </c>
+      <c r="D45" s="86"/>
       <c r="E45" s="59" t="e">
         <f>(C45-A45*1000000)/A45</f>
         <v>#VALUE!</v>
       </c>
       <c r="F45" s="59"/>
-      <c r="G45" s="63" t="s">
-        <v>11</v>
-      </c>
-      <c r="H45" s="64"/>
+      <c r="G45" s="89" t="s">
+        <v>10</v>
+      </c>
+      <c r="H45" s="90"/>
       <c r="I45" s="24"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -2229,17 +2204,17 @@
         <v>100</v>
       </c>
       <c r="B46" s="59"/>
-      <c r="C46" s="58" t="s">
-        <v>93</v>
-      </c>
-      <c r="D46" s="58"/>
+      <c r="C46" s="86" t="s">
+        <v>88</v>
+      </c>
+      <c r="D46" s="86"/>
       <c r="E46" s="59" t="e">
         <f t="shared" ref="E46:E54" si="0">(C46-A46*1000000)/A46</f>
         <v>#VALUE!</v>
       </c>
       <c r="F46" s="59"/>
-      <c r="G46" s="65"/>
-      <c r="H46" s="66"/>
+      <c r="G46" s="91"/>
+      <c r="H46" s="92"/>
       <c r="I46" s="24"/>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
@@ -2247,17 +2222,17 @@
         <v>250</v>
       </c>
       <c r="B47" s="59"/>
-      <c r="C47" s="58" t="s">
-        <v>94</v>
-      </c>
-      <c r="D47" s="58"/>
+      <c r="C47" s="86" t="s">
+        <v>89</v>
+      </c>
+      <c r="D47" s="86"/>
       <c r="E47" s="59" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="F47" s="59"/>
-      <c r="G47" s="65"/>
-      <c r="H47" s="66"/>
+      <c r="G47" s="91"/>
+      <c r="H47" s="92"/>
       <c r="I47" s="24"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
@@ -2265,17 +2240,17 @@
         <v>500</v>
       </c>
       <c r="B48" s="59"/>
-      <c r="C48" s="58" t="s">
-        <v>95</v>
-      </c>
-      <c r="D48" s="58"/>
+      <c r="C48" s="86" t="s">
+        <v>90</v>
+      </c>
+      <c r="D48" s="86"/>
       <c r="E48" s="59" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="F48" s="59"/>
-      <c r="G48" s="65"/>
-      <c r="H48" s="66"/>
+      <c r="G48" s="91"/>
+      <c r="H48" s="92"/>
       <c r="I48" s="24"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -2283,17 +2258,17 @@
         <v>1000</v>
       </c>
       <c r="B49" s="59"/>
-      <c r="C49" s="58" t="s">
-        <v>96</v>
-      </c>
-      <c r="D49" s="58"/>
+      <c r="C49" s="86" t="s">
+        <v>91</v>
+      </c>
+      <c r="D49" s="86"/>
       <c r="E49" s="59" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="F49" s="59"/>
-      <c r="G49" s="65"/>
-      <c r="H49" s="66"/>
+      <c r="G49" s="91"/>
+      <c r="H49" s="92"/>
       <c r="I49" s="24"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -2301,17 +2276,17 @@
         <v>2000</v>
       </c>
       <c r="B50" s="59"/>
-      <c r="C50" s="58" t="s">
-        <v>97</v>
-      </c>
-      <c r="D50" s="58"/>
+      <c r="C50" s="86" t="s">
+        <v>92</v>
+      </c>
+      <c r="D50" s="86"/>
       <c r="E50" s="59" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="F50" s="59"/>
-      <c r="G50" s="65"/>
-      <c r="H50" s="66"/>
+      <c r="G50" s="91"/>
+      <c r="H50" s="92"/>
       <c r="I50" s="24"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -2319,17 +2294,17 @@
         <v>4000</v>
       </c>
       <c r="B51" s="59"/>
-      <c r="C51" s="58" t="s">
-        <v>98</v>
-      </c>
-      <c r="D51" s="58"/>
+      <c r="C51" s="86" t="s">
+        <v>93</v>
+      </c>
+      <c r="D51" s="86"/>
       <c r="E51" s="59" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="F51" s="59"/>
-      <c r="G51" s="65"/>
-      <c r="H51" s="66"/>
+      <c r="G51" s="91"/>
+      <c r="H51" s="92"/>
       <c r="I51" s="24"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -2337,34 +2312,34 @@
         <v>8000</v>
       </c>
       <c r="B52" s="59"/>
-      <c r="C52" s="58" t="s">
-        <v>99</v>
-      </c>
-      <c r="D52" s="58"/>
+      <c r="C52" s="86" t="s">
+        <v>94</v>
+      </c>
+      <c r="D52" s="86"/>
       <c r="E52" s="59" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="F52" s="59"/>
-      <c r="G52" s="65"/>
-      <c r="H52" s="66"/>
+      <c r="G52" s="91"/>
+      <c r="H52" s="92"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="59">
         <v>16000</v>
       </c>
       <c r="B53" s="59"/>
-      <c r="C53" s="58" t="s">
-        <v>100</v>
-      </c>
-      <c r="D53" s="58"/>
+      <c r="C53" s="86" t="s">
+        <v>95</v>
+      </c>
+      <c r="D53" s="86"/>
       <c r="E53" s="59" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="F53" s="59"/>
-      <c r="G53" s="65"/>
-      <c r="H53" s="66"/>
+      <c r="G53" s="91"/>
+      <c r="H53" s="92"/>
       <c r="I53" s="17"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -2372,17 +2347,17 @@
         <v>20000</v>
       </c>
       <c r="B54" s="59"/>
-      <c r="C54" s="58" t="s">
-        <v>136</v>
-      </c>
-      <c r="D54" s="58"/>
+      <c r="C54" s="86" t="s">
+        <v>131</v>
+      </c>
+      <c r="D54" s="86"/>
       <c r="E54" s="59" t="e">
         <f t="shared" si="0"/>
         <v>#VALUE!</v>
       </c>
       <c r="F54" s="59"/>
-      <c r="G54" s="67"/>
-      <c r="H54" s="68"/>
+      <c r="G54" s="93"/>
+      <c r="H54" s="94"/>
       <c r="I54" s="17"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -2397,1460 +2372,1460 @@
       <c r="I55" s="17"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A56" s="60" t="s">
-        <v>58</v>
-      </c>
-      <c r="B56" s="60"/>
-      <c r="C56" s="60"/>
-      <c r="D56" s="60"/>
-      <c r="E56" s="60"/>
-      <c r="F56" s="60"/>
-      <c r="G56" s="60"/>
-      <c r="H56" s="60"/>
-      <c r="I56" s="60"/>
+      <c r="A56" s="95" t="s">
+        <v>53</v>
+      </c>
+      <c r="B56" s="95"/>
+      <c r="C56" s="95"/>
+      <c r="D56" s="95"/>
+      <c r="E56" s="95"/>
+      <c r="F56" s="95"/>
+      <c r="G56" s="95"/>
+      <c r="H56" s="95"/>
+      <c r="I56" s="95"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57" s="60"/>
-      <c r="B57" s="60"/>
-      <c r="C57" s="60"/>
-      <c r="D57" s="60"/>
-      <c r="E57" s="60"/>
-      <c r="F57" s="60"/>
-      <c r="G57" s="60"/>
-      <c r="H57" s="60"/>
-      <c r="I57" s="60"/>
+      <c r="A57" s="95"/>
+      <c r="B57" s="95"/>
+      <c r="C57" s="95"/>
+      <c r="D57" s="95"/>
+      <c r="E57" s="95"/>
+      <c r="F57" s="95"/>
+      <c r="G57" s="95"/>
+      <c r="H57" s="95"/>
+      <c r="I57" s="95"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B58" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="C58" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="C58" s="52" t="s">
+      <c r="D58" s="48"/>
+      <c r="E58" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="D58" s="52"/>
-      <c r="E58" s="52" t="s">
+      <c r="F58" s="48"/>
+      <c r="G58" s="3" t="s">
         <v>7</v>
-      </c>
-      <c r="F58" s="52"/>
-      <c r="G58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H58" s="17"/>
       <c r="I58" s="17"/>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59" s="52">
+      <c r="A59" s="48">
         <v>50</v>
       </c>
       <c r="B59" s="29">
         <v>10</v>
       </c>
-      <c r="C59" s="48" t="s">
-        <v>101</v>
-      </c>
-      <c r="D59" s="48"/>
-      <c r="E59" s="50" t="e">
+      <c r="C59" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="D59" s="50"/>
+      <c r="E59" s="51" t="e">
         <f>B59-C59</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F59" s="50"/>
-      <c r="G59" s="54" t="s">
-        <v>12</v>
+      <c r="F59" s="51"/>
+      <c r="G59" s="49" t="s">
+        <v>11</v>
       </c>
       <c r="H59" s="17"/>
       <c r="I59" s="17"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60" s="52"/>
+      <c r="A60" s="48"/>
       <c r="B60" s="29">
         <v>0</v>
       </c>
-      <c r="C60" s="48" t="s">
-        <v>102</v>
-      </c>
-      <c r="D60" s="48"/>
-      <c r="E60" s="50" t="e">
+      <c r="C60" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="D60" s="50"/>
+      <c r="E60" s="51" t="e">
         <f t="shared" ref="E60:E123" si="1">B60-C60</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F60" s="50"/>
-      <c r="G60" s="54"/>
+      <c r="F60" s="51"/>
+      <c r="G60" s="49"/>
       <c r="H60" s="17"/>
       <c r="I60" s="17"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" s="52"/>
+      <c r="A61" s="48"/>
       <c r="B61" s="30">
         <v>-10</v>
       </c>
-      <c r="C61" s="48" t="s">
-        <v>103</v>
-      </c>
-      <c r="D61" s="48"/>
-      <c r="E61" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F61" s="50"/>
-      <c r="G61" s="54"/>
+      <c r="C61" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="D61" s="50"/>
+      <c r="E61" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F61" s="51"/>
+      <c r="G61" s="49"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62" s="52"/>
+      <c r="A62" s="48"/>
       <c r="B62" s="30">
         <v>-20</v>
       </c>
-      <c r="C62" s="48" t="s">
-        <v>104</v>
-      </c>
-      <c r="D62" s="48"/>
-      <c r="E62" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F62" s="50"/>
-      <c r="G62" s="54"/>
+      <c r="C62" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="D62" s="50"/>
+      <c r="E62" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F62" s="51"/>
+      <c r="G62" s="49"/>
       <c r="H62" s="4"/>
       <c r="L62" s="11"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63" s="52"/>
+      <c r="A63" s="48"/>
       <c r="B63" s="30">
         <v>-30</v>
       </c>
-      <c r="C63" s="48" t="s">
-        <v>105</v>
-      </c>
-      <c r="D63" s="48"/>
-      <c r="E63" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F63" s="50"/>
-      <c r="G63" s="54" t="s">
-        <v>44</v>
+      <c r="C63" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="D63" s="50"/>
+      <c r="E63" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F63" s="51"/>
+      <c r="G63" s="49" t="s">
+        <v>39</v>
       </c>
       <c r="H63" s="26"/>
     </row>
     <row r="64" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="52"/>
+      <c r="A64" s="48"/>
       <c r="B64" s="30">
         <v>-40</v>
       </c>
-      <c r="C64" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="D64" s="48"/>
-      <c r="E64" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F64" s="50"/>
-      <c r="G64" s="54"/>
+      <c r="C64" s="50" t="s">
+        <v>173</v>
+      </c>
+      <c r="D64" s="50"/>
+      <c r="E64" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F64" s="51"/>
+      <c r="G64" s="49"/>
       <c r="H64" s="26"/>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="52"/>
+      <c r="A65" s="48"/>
       <c r="B65" s="30">
         <v>-50</v>
       </c>
-      <c r="C65" s="48" t="s">
-        <v>179</v>
-      </c>
-      <c r="D65" s="48"/>
-      <c r="E65" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F65" s="50"/>
-      <c r="G65" s="54"/>
+      <c r="C65" s="50" t="s">
+        <v>174</v>
+      </c>
+      <c r="D65" s="50"/>
+      <c r="E65" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F65" s="51"/>
+      <c r="G65" s="49"/>
       <c r="H65" s="10"/>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="52"/>
+      <c r="A66" s="48"/>
       <c r="B66" s="30">
         <v>-60</v>
       </c>
-      <c r="C66" s="48" t="s">
-        <v>180</v>
-      </c>
-      <c r="D66" s="48"/>
-      <c r="E66" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F66" s="50"/>
-      <c r="G66" s="54"/>
+      <c r="C66" s="50" t="s">
+        <v>175</v>
+      </c>
+      <c r="D66" s="50"/>
+      <c r="E66" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F66" s="51"/>
+      <c r="G66" s="49"/>
       <c r="H66" s="10"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="52"/>
+      <c r="A67" s="48"/>
       <c r="B67" s="30">
         <v>-70</v>
       </c>
-      <c r="C67" s="48" t="s">
-        <v>181</v>
-      </c>
-      <c r="D67" s="48"/>
-      <c r="E67" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F67" s="50"/>
-      <c r="G67" s="54"/>
+      <c r="C67" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="D67" s="50"/>
+      <c r="E67" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F67" s="51"/>
+      <c r="G67" s="49"/>
       <c r="H67" s="10"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="52"/>
+      <c r="A68" s="48"/>
       <c r="B68" s="30">
         <v>-80</v>
       </c>
-      <c r="C68" s="48" t="s">
-        <v>182</v>
-      </c>
-      <c r="D68" s="48"/>
-      <c r="E68" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F68" s="50"/>
-      <c r="G68" s="54"/>
+      <c r="C68" s="50" t="s">
+        <v>177</v>
+      </c>
+      <c r="D68" s="50"/>
+      <c r="E68" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F68" s="51"/>
+      <c r="G68" s="49"/>
       <c r="H68" s="10"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="52"/>
+      <c r="A69" s="48"/>
       <c r="B69" s="30">
         <v>-90</v>
       </c>
-      <c r="C69" s="48" t="s">
-        <v>183</v>
-      </c>
-      <c r="D69" s="48"/>
-      <c r="E69" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F69" s="50"/>
-      <c r="G69" s="54"/>
+      <c r="C69" s="50" t="s">
+        <v>178</v>
+      </c>
+      <c r="D69" s="50"/>
+      <c r="E69" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F69" s="51"/>
+      <c r="G69" s="49"/>
       <c r="H69" s="10"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="52">
+      <c r="A70" s="48">
         <v>1000</v>
       </c>
       <c r="B70" s="29">
         <v>10</v>
       </c>
-      <c r="C70" s="48" t="s">
-        <v>106</v>
-      </c>
-      <c r="D70" s="48"/>
-      <c r="E70" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F70" s="50"/>
-      <c r="G70" s="54" t="s">
-        <v>12</v>
+      <c r="C70" s="50" t="s">
+        <v>101</v>
+      </c>
+      <c r="D70" s="50"/>
+      <c r="E70" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F70" s="51"/>
+      <c r="G70" s="49" t="s">
+        <v>11</v>
       </c>
       <c r="H70" s="10"/>
       <c r="I70" s="17"/>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="52"/>
+      <c r="A71" s="48"/>
       <c r="B71" s="29">
         <v>0</v>
       </c>
-      <c r="C71" s="48" t="s">
-        <v>107</v>
-      </c>
-      <c r="D71" s="48"/>
-      <c r="E71" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F71" s="50"/>
-      <c r="G71" s="54"/>
+      <c r="C71" s="50" t="s">
+        <v>102</v>
+      </c>
+      <c r="D71" s="50"/>
+      <c r="E71" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F71" s="51"/>
+      <c r="G71" s="49"/>
       <c r="H71" s="10"/>
       <c r="I71" s="17"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="52"/>
+      <c r="A72" s="48"/>
       <c r="B72" s="30">
         <v>-10</v>
       </c>
-      <c r="C72" s="48" t="s">
-        <v>108</v>
-      </c>
-      <c r="D72" s="48"/>
-      <c r="E72" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F72" s="50"/>
-      <c r="G72" s="54"/>
+      <c r="C72" s="50" t="s">
+        <v>103</v>
+      </c>
+      <c r="D72" s="50"/>
+      <c r="E72" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F72" s="51"/>
+      <c r="G72" s="49"/>
       <c r="H72" s="10"/>
       <c r="I72" s="17"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="52"/>
+      <c r="A73" s="48"/>
       <c r="B73" s="30">
         <v>-20</v>
       </c>
-      <c r="C73" s="48" t="s">
-        <v>109</v>
-      </c>
-      <c r="D73" s="48"/>
-      <c r="E73" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F73" s="50"/>
-      <c r="G73" s="54"/>
+      <c r="C73" s="50" t="s">
+        <v>104</v>
+      </c>
+      <c r="D73" s="50"/>
+      <c r="E73" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F73" s="51"/>
+      <c r="G73" s="49"/>
       <c r="H73" s="10"/>
       <c r="I73" s="17"/>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="52"/>
+      <c r="A74" s="48"/>
       <c r="B74" s="30">
         <v>-30</v>
       </c>
-      <c r="C74" s="48" t="s">
-        <v>110</v>
-      </c>
-      <c r="D74" s="48"/>
-      <c r="E74" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F74" s="50"/>
-      <c r="G74" s="54" t="s">
-        <v>44</v>
+      <c r="C74" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="D74" s="50"/>
+      <c r="E74" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F74" s="51"/>
+      <c r="G74" s="49" t="s">
+        <v>39</v>
       </c>
       <c r="H74" s="10"/>
       <c r="I74" s="17"/>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" s="52"/>
+      <c r="A75" s="48"/>
       <c r="B75" s="30">
         <v>-40</v>
       </c>
-      <c r="C75" s="48" t="s">
-        <v>197</v>
-      </c>
-      <c r="D75" s="48"/>
-      <c r="E75" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F75" s="50"/>
-      <c r="G75" s="54"/>
+      <c r="C75" s="50" t="s">
+        <v>192</v>
+      </c>
+      <c r="D75" s="50"/>
+      <c r="E75" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F75" s="51"/>
+      <c r="G75" s="49"/>
       <c r="H75" s="10"/>
       <c r="I75" s="17"/>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" s="52"/>
+      <c r="A76" s="48"/>
       <c r="B76" s="30">
         <v>-50</v>
       </c>
-      <c r="C76" s="48" t="s">
-        <v>198</v>
-      </c>
-      <c r="D76" s="48"/>
-      <c r="E76" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F76" s="50"/>
-      <c r="G76" s="54"/>
+      <c r="C76" s="50" t="s">
+        <v>193</v>
+      </c>
+      <c r="D76" s="50"/>
+      <c r="E76" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F76" s="51"/>
+      <c r="G76" s="49"/>
       <c r="H76" s="10"/>
       <c r="I76" s="17"/>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A77" s="52"/>
+      <c r="A77" s="48"/>
       <c r="B77" s="30">
         <v>-60</v>
       </c>
-      <c r="C77" s="48" t="s">
-        <v>199</v>
-      </c>
-      <c r="D77" s="48"/>
-      <c r="E77" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F77" s="50"/>
-      <c r="G77" s="54"/>
+      <c r="C77" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="D77" s="50"/>
+      <c r="E77" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F77" s="51"/>
+      <c r="G77" s="49"/>
       <c r="H77" s="10"/>
       <c r="I77" s="17"/>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="52"/>
+      <c r="A78" s="48"/>
       <c r="B78" s="30">
         <v>-70</v>
       </c>
-      <c r="C78" s="48" t="s">
-        <v>200</v>
-      </c>
-      <c r="D78" s="48"/>
-      <c r="E78" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F78" s="50"/>
-      <c r="G78" s="54"/>
+      <c r="C78" s="50" t="s">
+        <v>195</v>
+      </c>
+      <c r="D78" s="50"/>
+      <c r="E78" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F78" s="51"/>
+      <c r="G78" s="49"/>
       <c r="H78" s="10"/>
       <c r="I78" s="17"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="52"/>
+      <c r="A79" s="48"/>
       <c r="B79" s="30">
         <v>-80</v>
       </c>
-      <c r="C79" s="48" t="s">
-        <v>201</v>
-      </c>
-      <c r="D79" s="48"/>
-      <c r="E79" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F79" s="50"/>
-      <c r="G79" s="54"/>
+      <c r="C79" s="50" t="s">
+        <v>196</v>
+      </c>
+      <c r="D79" s="50"/>
+      <c r="E79" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F79" s="51"/>
+      <c r="G79" s="49"/>
       <c r="H79" s="10"/>
       <c r="I79" s="17"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" s="52"/>
+      <c r="A80" s="48"/>
       <c r="B80" s="30">
         <v>-90</v>
       </c>
-      <c r="C80" s="48" t="s">
-        <v>184</v>
-      </c>
-      <c r="D80" s="48"/>
-      <c r="E80" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F80" s="50"/>
-      <c r="G80" s="54"/>
+      <c r="C80" s="50" t="s">
+        <v>179</v>
+      </c>
+      <c r="D80" s="50"/>
+      <c r="E80" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F80" s="51"/>
+      <c r="G80" s="49"/>
       <c r="H80" s="10"/>
       <c r="I80" s="17"/>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="52">
+      <c r="A81" s="48">
         <v>2000</v>
       </c>
       <c r="B81" s="29">
         <v>10</v>
       </c>
-      <c r="C81" s="48" t="s">
-        <v>111</v>
-      </c>
-      <c r="D81" s="48"/>
-      <c r="E81" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F81" s="50"/>
-      <c r="G81" s="54" t="s">
-        <v>12</v>
+      <c r="C81" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="D81" s="50"/>
+      <c r="E81" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F81" s="51"/>
+      <c r="G81" s="49" t="s">
+        <v>11</v>
       </c>
       <c r="H81" s="10"/>
       <c r="I81" s="17"/>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" s="52"/>
+      <c r="A82" s="48"/>
       <c r="B82" s="29">
         <v>0</v>
       </c>
-      <c r="C82" s="48" t="s">
-        <v>112</v>
-      </c>
-      <c r="D82" s="48"/>
-      <c r="E82" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F82" s="50"/>
-      <c r="G82" s="54"/>
+      <c r="C82" s="50" t="s">
+        <v>107</v>
+      </c>
+      <c r="D82" s="50"/>
+      <c r="E82" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F82" s="51"/>
+      <c r="G82" s="49"/>
       <c r="H82" s="10"/>
       <c r="I82" s="17"/>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A83" s="52"/>
+      <c r="A83" s="48"/>
       <c r="B83" s="30">
         <v>-10</v>
       </c>
-      <c r="C83" s="48" t="s">
-        <v>113</v>
-      </c>
-      <c r="D83" s="48"/>
-      <c r="E83" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F83" s="50"/>
-      <c r="G83" s="54"/>
+      <c r="C83" s="50" t="s">
+        <v>108</v>
+      </c>
+      <c r="D83" s="50"/>
+      <c r="E83" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F83" s="51"/>
+      <c r="G83" s="49"/>
       <c r="H83" s="10"/>
       <c r="I83" s="17"/>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84" s="52"/>
+      <c r="A84" s="48"/>
       <c r="B84" s="30">
         <v>-20</v>
       </c>
-      <c r="C84" s="48" t="s">
-        <v>114</v>
-      </c>
-      <c r="D84" s="48"/>
-      <c r="E84" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F84" s="50"/>
-      <c r="G84" s="54"/>
+      <c r="C84" s="50" t="s">
+        <v>109</v>
+      </c>
+      <c r="D84" s="50"/>
+      <c r="E84" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F84" s="51"/>
+      <c r="G84" s="49"/>
       <c r="H84" s="10"/>
       <c r="I84" s="17"/>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A85" s="52"/>
+      <c r="A85" s="48"/>
       <c r="B85" s="30">
         <v>-30</v>
       </c>
-      <c r="C85" s="48" t="s">
-        <v>115</v>
-      </c>
-      <c r="D85" s="48"/>
-      <c r="E85" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F85" s="50"/>
-      <c r="G85" s="54" t="s">
-        <v>44</v>
+      <c r="C85" s="50" t="s">
+        <v>110</v>
+      </c>
+      <c r="D85" s="50"/>
+      <c r="E85" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F85" s="51"/>
+      <c r="G85" s="49" t="s">
+        <v>39</v>
       </c>
       <c r="H85" s="10"/>
       <c r="I85" s="17"/>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" s="52"/>
+      <c r="A86" s="48"/>
       <c r="B86" s="30">
         <v>-40</v>
       </c>
-      <c r="C86" s="48" t="s">
-        <v>192</v>
-      </c>
-      <c r="D86" s="48"/>
-      <c r="E86" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F86" s="50"/>
-      <c r="G86" s="54"/>
+      <c r="C86" s="50" t="s">
+        <v>187</v>
+      </c>
+      <c r="D86" s="50"/>
+      <c r="E86" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F86" s="51"/>
+      <c r="G86" s="49"/>
       <c r="H86" s="10"/>
       <c r="I86" s="17"/>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" s="52"/>
+      <c r="A87" s="48"/>
       <c r="B87" s="30">
         <v>-50</v>
       </c>
-      <c r="C87" s="48" t="s">
-        <v>193</v>
-      </c>
-      <c r="D87" s="48"/>
-      <c r="E87" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F87" s="50"/>
-      <c r="G87" s="54"/>
+      <c r="C87" s="50" t="s">
+        <v>188</v>
+      </c>
+      <c r="D87" s="50"/>
+      <c r="E87" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F87" s="51"/>
+      <c r="G87" s="49"/>
       <c r="H87" s="10"/>
       <c r="I87" s="17"/>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88" s="52"/>
+      <c r="A88" s="48"/>
       <c r="B88" s="30">
         <v>-60</v>
       </c>
-      <c r="C88" s="48" t="s">
-        <v>194</v>
-      </c>
-      <c r="D88" s="48"/>
-      <c r="E88" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F88" s="50"/>
-      <c r="G88" s="54"/>
+      <c r="C88" s="50" t="s">
+        <v>189</v>
+      </c>
+      <c r="D88" s="50"/>
+      <c r="E88" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F88" s="51"/>
+      <c r="G88" s="49"/>
       <c r="H88" s="10"/>
       <c r="I88" s="17"/>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" s="52"/>
+      <c r="A89" s="48"/>
       <c r="B89" s="30">
         <v>-70</v>
       </c>
-      <c r="C89" s="48" t="s">
-        <v>195</v>
-      </c>
-      <c r="D89" s="48"/>
-      <c r="E89" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F89" s="50"/>
-      <c r="G89" s="54"/>
+      <c r="C89" s="50" t="s">
+        <v>190</v>
+      </c>
+      <c r="D89" s="50"/>
+      <c r="E89" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F89" s="51"/>
+      <c r="G89" s="49"/>
       <c r="H89" s="10"/>
       <c r="I89" s="17"/>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" s="52"/>
+      <c r="A90" s="48"/>
       <c r="B90" s="30">
         <v>-80</v>
       </c>
-      <c r="C90" s="48" t="s">
-        <v>196</v>
-      </c>
-      <c r="D90" s="48"/>
-      <c r="E90" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F90" s="50"/>
-      <c r="G90" s="54"/>
+      <c r="C90" s="50" t="s">
+        <v>191</v>
+      </c>
+      <c r="D90" s="50"/>
+      <c r="E90" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F90" s="51"/>
+      <c r="G90" s="49"/>
       <c r="H90" s="10"/>
       <c r="I90" s="17"/>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A91" s="52"/>
+      <c r="A91" s="48"/>
       <c r="B91" s="30">
         <v>-90</v>
       </c>
-      <c r="C91" s="48" t="s">
-        <v>185</v>
-      </c>
-      <c r="D91" s="48"/>
-      <c r="E91" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F91" s="50"/>
-      <c r="G91" s="54"/>
+      <c r="C91" s="50" t="s">
+        <v>180</v>
+      </c>
+      <c r="D91" s="50"/>
+      <c r="E91" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F91" s="51"/>
+      <c r="G91" s="49"/>
       <c r="H91" s="10"/>
       <c r="I91" s="17"/>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92" s="52">
+      <c r="A92" s="48">
         <v>4000</v>
       </c>
       <c r="B92" s="29">
         <v>10</v>
       </c>
-      <c r="C92" s="48" t="s">
-        <v>116</v>
-      </c>
-      <c r="D92" s="48"/>
-      <c r="E92" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F92" s="50"/>
-      <c r="G92" s="54" t="s">
-        <v>12</v>
+      <c r="C92" s="50" t="s">
+        <v>111</v>
+      </c>
+      <c r="D92" s="50"/>
+      <c r="E92" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F92" s="51"/>
+      <c r="G92" s="49" t="s">
+        <v>11</v>
       </c>
       <c r="H92" s="10"/>
       <c r="I92" s="17"/>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A93" s="52"/>
+      <c r="A93" s="48"/>
       <c r="B93" s="29">
         <v>0</v>
       </c>
-      <c r="C93" s="48" t="s">
-        <v>117</v>
-      </c>
-      <c r="D93" s="48"/>
-      <c r="E93" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F93" s="50"/>
-      <c r="G93" s="54"/>
+      <c r="C93" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="D93" s="50"/>
+      <c r="E93" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F93" s="51"/>
+      <c r="G93" s="49"/>
       <c r="H93" s="10"/>
       <c r="I93" s="17"/>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A94" s="52"/>
+      <c r="A94" s="48"/>
       <c r="B94" s="30">
         <v>-10</v>
       </c>
-      <c r="C94" s="48" t="s">
-        <v>118</v>
-      </c>
-      <c r="D94" s="48"/>
-      <c r="E94" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F94" s="50"/>
-      <c r="G94" s="54"/>
+      <c r="C94" s="50" t="s">
+        <v>113</v>
+      </c>
+      <c r="D94" s="50"/>
+      <c r="E94" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F94" s="51"/>
+      <c r="G94" s="49"/>
       <c r="H94" s="10"/>
       <c r="I94" s="17"/>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A95" s="52"/>
+      <c r="A95" s="48"/>
       <c r="B95" s="30">
         <v>-20</v>
       </c>
-      <c r="C95" s="48" t="s">
-        <v>119</v>
-      </c>
-      <c r="D95" s="48"/>
-      <c r="E95" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F95" s="50"/>
-      <c r="G95" s="54"/>
+      <c r="C95" s="50" t="s">
+        <v>114</v>
+      </c>
+      <c r="D95" s="50"/>
+      <c r="E95" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F95" s="51"/>
+      <c r="G95" s="49"/>
       <c r="H95" s="10"/>
       <c r="I95" s="17"/>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" s="52"/>
+      <c r="A96" s="48"/>
       <c r="B96" s="30">
         <v>-30</v>
       </c>
-      <c r="C96" s="48" t="s">
-        <v>120</v>
-      </c>
-      <c r="D96" s="48"/>
-      <c r="E96" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F96" s="50"/>
-      <c r="G96" s="54" t="s">
-        <v>44</v>
+      <c r="C96" s="50" t="s">
+        <v>115</v>
+      </c>
+      <c r="D96" s="50"/>
+      <c r="E96" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F96" s="51"/>
+      <c r="G96" s="49" t="s">
+        <v>39</v>
       </c>
       <c r="H96" s="10"/>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" s="52"/>
+      <c r="A97" s="48"/>
       <c r="B97" s="30">
         <v>-40</v>
       </c>
-      <c r="C97" s="48" t="s">
-        <v>187</v>
-      </c>
-      <c r="D97" s="48"/>
-      <c r="E97" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F97" s="50"/>
-      <c r="G97" s="54"/>
+      <c r="C97" s="50" t="s">
+        <v>182</v>
+      </c>
+      <c r="D97" s="50"/>
+      <c r="E97" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F97" s="51"/>
+      <c r="G97" s="49"/>
       <c r="H97" s="10"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98" s="52"/>
+      <c r="A98" s="48"/>
       <c r="B98" s="30">
         <v>-50</v>
       </c>
-      <c r="C98" s="48" t="s">
-        <v>188</v>
-      </c>
-      <c r="D98" s="48"/>
-      <c r="E98" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F98" s="50"/>
-      <c r="G98" s="54"/>
+      <c r="C98" s="50" t="s">
+        <v>183</v>
+      </c>
+      <c r="D98" s="50"/>
+      <c r="E98" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F98" s="51"/>
+      <c r="G98" s="49"/>
       <c r="H98" s="10"/>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A99" s="52"/>
+      <c r="A99" s="48"/>
       <c r="B99" s="30">
         <v>-60</v>
       </c>
-      <c r="C99" s="48" t="s">
-        <v>189</v>
-      </c>
-      <c r="D99" s="48"/>
-      <c r="E99" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F99" s="50"/>
-      <c r="G99" s="54"/>
+      <c r="C99" s="50" t="s">
+        <v>184</v>
+      </c>
+      <c r="D99" s="50"/>
+      <c r="E99" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F99" s="51"/>
+      <c r="G99" s="49"/>
       <c r="H99" s="10"/>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100" s="52"/>
+      <c r="A100" s="48"/>
       <c r="B100" s="30">
         <v>-70</v>
       </c>
-      <c r="C100" s="48" t="s">
-        <v>190</v>
-      </c>
-      <c r="D100" s="48"/>
-      <c r="E100" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F100" s="50"/>
-      <c r="G100" s="54"/>
+      <c r="C100" s="50" t="s">
+        <v>185</v>
+      </c>
+      <c r="D100" s="50"/>
+      <c r="E100" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F100" s="51"/>
+      <c r="G100" s="49"/>
       <c r="H100" s="10"/>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A101" s="52"/>
+      <c r="A101" s="48"/>
       <c r="B101" s="30">
         <v>-80</v>
       </c>
-      <c r="C101" s="48" t="s">
-        <v>191</v>
-      </c>
-      <c r="D101" s="48"/>
-      <c r="E101" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F101" s="50"/>
-      <c r="G101" s="54"/>
+      <c r="C101" s="50" t="s">
+        <v>186</v>
+      </c>
+      <c r="D101" s="50"/>
+      <c r="E101" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F101" s="51"/>
+      <c r="G101" s="49"/>
       <c r="H101" s="16"/>
       <c r="I101" s="14"/>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A102" s="52"/>
+      <c r="A102" s="48"/>
       <c r="B102" s="30">
         <v>-90</v>
       </c>
-      <c r="C102" s="48" t="s">
-        <v>186</v>
-      </c>
-      <c r="D102" s="48"/>
-      <c r="E102" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F102" s="50"/>
-      <c r="G102" s="54"/>
+      <c r="C102" s="50" t="s">
+        <v>181</v>
+      </c>
+      <c r="D102" s="50"/>
+      <c r="E102" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F102" s="51"/>
+      <c r="G102" s="49"/>
       <c r="H102" s="8"/>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A103" s="52">
+      <c r="A103" s="48">
         <v>8000</v>
       </c>
       <c r="B103" s="29">
         <v>10</v>
       </c>
-      <c r="C103" s="48" t="s">
-        <v>121</v>
-      </c>
-      <c r="D103" s="48"/>
-      <c r="E103" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F103" s="50"/>
-      <c r="G103" s="54" t="s">
-        <v>12</v>
+      <c r="C103" s="50" t="s">
+        <v>116</v>
+      </c>
+      <c r="D103" s="50"/>
+      <c r="E103" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F103" s="51"/>
+      <c r="G103" s="49" t="s">
+        <v>11</v>
       </c>
       <c r="H103" s="17"/>
       <c r="I103" s="17"/>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" s="52"/>
+      <c r="A104" s="48"/>
       <c r="B104" s="29">
         <v>0</v>
       </c>
-      <c r="C104" s="48" t="s">
-        <v>122</v>
-      </c>
-      <c r="D104" s="48"/>
-      <c r="E104" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F104" s="50"/>
-      <c r="G104" s="54"/>
+      <c r="C104" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="D104" s="50"/>
+      <c r="E104" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F104" s="51"/>
+      <c r="G104" s="49"/>
       <c r="H104" s="17"/>
       <c r="I104" s="17"/>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A105" s="52"/>
+      <c r="A105" s="48"/>
       <c r="B105" s="30">
         <v>-10</v>
       </c>
-      <c r="C105" s="48" t="s">
-        <v>123</v>
-      </c>
-      <c r="D105" s="48"/>
-      <c r="E105" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F105" s="50"/>
-      <c r="G105" s="54"/>
+      <c r="C105" s="50" t="s">
+        <v>118</v>
+      </c>
+      <c r="D105" s="50"/>
+      <c r="E105" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F105" s="51"/>
+      <c r="G105" s="49"/>
       <c r="H105" s="17"/>
       <c r="I105" s="17"/>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A106" s="52"/>
+      <c r="A106" s="48"/>
       <c r="B106" s="30">
         <v>-20</v>
       </c>
-      <c r="C106" s="48" t="s">
-        <v>124</v>
-      </c>
-      <c r="D106" s="48"/>
-      <c r="E106" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F106" s="50"/>
-      <c r="G106" s="54"/>
+      <c r="C106" s="50" t="s">
+        <v>119</v>
+      </c>
+      <c r="D106" s="50"/>
+      <c r="E106" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F106" s="51"/>
+      <c r="G106" s="49"/>
       <c r="H106" s="17"/>
       <c r="I106" s="17"/>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A107" s="52"/>
+      <c r="A107" s="48"/>
       <c r="B107" s="30">
         <v>-30</v>
       </c>
-      <c r="C107" s="48" t="s">
-        <v>125</v>
-      </c>
-      <c r="D107" s="48"/>
-      <c r="E107" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F107" s="50"/>
-      <c r="G107" s="54" t="s">
-        <v>44</v>
+      <c r="C107" s="50" t="s">
+        <v>120</v>
+      </c>
+      <c r="D107" s="50"/>
+      <c r="E107" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F107" s="51"/>
+      <c r="G107" s="49" t="s">
+        <v>39</v>
       </c>
       <c r="H107" s="17"/>
       <c r="I107" s="17"/>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A108" s="52"/>
+      <c r="A108" s="48"/>
       <c r="B108" s="30">
         <v>-40</v>
       </c>
-      <c r="C108" s="48" t="s">
-        <v>202</v>
-      </c>
-      <c r="D108" s="48"/>
-      <c r="E108" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F108" s="50"/>
-      <c r="G108" s="54"/>
+      <c r="C108" s="50" t="s">
+        <v>197</v>
+      </c>
+      <c r="D108" s="50"/>
+      <c r="E108" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F108" s="51"/>
+      <c r="G108" s="49"/>
       <c r="H108" s="17"/>
       <c r="I108" s="17"/>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="52"/>
+      <c r="A109" s="48"/>
       <c r="B109" s="30">
         <v>-50</v>
       </c>
-      <c r="C109" s="48" t="s">
-        <v>203</v>
-      </c>
-      <c r="D109" s="48"/>
-      <c r="E109" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F109" s="50"/>
-      <c r="G109" s="54"/>
+      <c r="C109" s="50" t="s">
+        <v>198</v>
+      </c>
+      <c r="D109" s="50"/>
+      <c r="E109" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F109" s="51"/>
+      <c r="G109" s="49"/>
       <c r="H109" s="17"/>
       <c r="I109" s="17"/>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110" s="52"/>
+      <c r="A110" s="48"/>
       <c r="B110" s="30">
         <v>-60</v>
       </c>
-      <c r="C110" s="48" t="s">
-        <v>204</v>
-      </c>
-      <c r="D110" s="48"/>
-      <c r="E110" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F110" s="50"/>
-      <c r="G110" s="54"/>
+      <c r="C110" s="50" t="s">
+        <v>199</v>
+      </c>
+      <c r="D110" s="50"/>
+      <c r="E110" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F110" s="51"/>
+      <c r="G110" s="49"/>
       <c r="H110" s="17"/>
       <c r="I110" s="17"/>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" s="52"/>
+      <c r="A111" s="48"/>
       <c r="B111" s="30">
         <v>-70</v>
       </c>
-      <c r="C111" s="48" t="s">
-        <v>205</v>
-      </c>
-      <c r="D111" s="48"/>
-      <c r="E111" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F111" s="50"/>
-      <c r="G111" s="54"/>
+      <c r="C111" s="50" t="s">
+        <v>200</v>
+      </c>
+      <c r="D111" s="50"/>
+      <c r="E111" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F111" s="51"/>
+      <c r="G111" s="49"/>
       <c r="H111" s="17"/>
       <c r="I111" s="17"/>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112" s="52"/>
+      <c r="A112" s="48"/>
       <c r="B112" s="30">
         <v>-80</v>
       </c>
-      <c r="C112" s="48" t="s">
-        <v>206</v>
-      </c>
-      <c r="D112" s="48"/>
-      <c r="E112" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F112" s="50"/>
-      <c r="G112" s="54"/>
+      <c r="C112" s="50" t="s">
+        <v>201</v>
+      </c>
+      <c r="D112" s="50"/>
+      <c r="E112" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F112" s="51"/>
+      <c r="G112" s="49"/>
       <c r="H112" s="17"/>
       <c r="I112" s="17"/>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A113" s="52"/>
+      <c r="A113" s="48"/>
       <c r="B113" s="30">
         <v>-90</v>
       </c>
-      <c r="C113" s="48" t="s">
-        <v>207</v>
-      </c>
-      <c r="D113" s="48"/>
-      <c r="E113" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F113" s="50"/>
-      <c r="G113" s="54"/>
+      <c r="C113" s="50" t="s">
+        <v>202</v>
+      </c>
+      <c r="D113" s="50"/>
+      <c r="E113" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F113" s="51"/>
+      <c r="G113" s="49"/>
       <c r="H113" s="17"/>
       <c r="I113" s="17"/>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A114" s="52">
+      <c r="A114" s="48">
         <v>16000</v>
       </c>
       <c r="B114" s="29">
         <v>10</v>
       </c>
-      <c r="C114" s="48" t="s">
-        <v>126</v>
-      </c>
-      <c r="D114" s="48"/>
-      <c r="E114" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F114" s="50"/>
-      <c r="G114" s="54" t="s">
-        <v>12</v>
+      <c r="C114" s="50" t="s">
+        <v>121</v>
+      </c>
+      <c r="D114" s="50"/>
+      <c r="E114" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F114" s="51"/>
+      <c r="G114" s="49" t="s">
+        <v>11</v>
       </c>
       <c r="H114" s="17"/>
       <c r="I114" s="17"/>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A115" s="52"/>
+      <c r="A115" s="48"/>
       <c r="B115" s="29">
         <v>0</v>
       </c>
-      <c r="C115" s="48" t="s">
-        <v>127</v>
-      </c>
-      <c r="D115" s="48"/>
-      <c r="E115" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F115" s="50"/>
-      <c r="G115" s="54"/>
+      <c r="C115" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="D115" s="50"/>
+      <c r="E115" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F115" s="51"/>
+      <c r="G115" s="49"/>
       <c r="H115" s="17"/>
       <c r="I115" s="17"/>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A116" s="52"/>
+      <c r="A116" s="48"/>
       <c r="B116" s="30">
         <v>-10</v>
       </c>
-      <c r="C116" s="48" t="s">
-        <v>128</v>
-      </c>
-      <c r="D116" s="48"/>
-      <c r="E116" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F116" s="50"/>
-      <c r="G116" s="54"/>
+      <c r="C116" s="50" t="s">
+        <v>123</v>
+      </c>
+      <c r="D116" s="50"/>
+      <c r="E116" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F116" s="51"/>
+      <c r="G116" s="49"/>
       <c r="H116" s="17"/>
       <c r="I116" s="17"/>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A117" s="52"/>
+      <c r="A117" s="48"/>
       <c r="B117" s="30">
         <v>-20</v>
       </c>
-      <c r="C117" s="48" t="s">
-        <v>129</v>
-      </c>
-      <c r="D117" s="48"/>
-      <c r="E117" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F117" s="50"/>
-      <c r="G117" s="54"/>
+      <c r="C117" s="50" t="s">
+        <v>124</v>
+      </c>
+      <c r="D117" s="50"/>
+      <c r="E117" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F117" s="51"/>
+      <c r="G117" s="49"/>
       <c r="H117" s="17"/>
       <c r="I117" s="17"/>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A118" s="52"/>
+      <c r="A118" s="48"/>
       <c r="B118" s="30">
         <v>-30</v>
       </c>
-      <c r="C118" s="48" t="s">
-        <v>130</v>
-      </c>
-      <c r="D118" s="48"/>
-      <c r="E118" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F118" s="50"/>
-      <c r="G118" s="54" t="s">
-        <v>44</v>
+      <c r="C118" s="50" t="s">
+        <v>125</v>
+      </c>
+      <c r="D118" s="50"/>
+      <c r="E118" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F118" s="51"/>
+      <c r="G118" s="49" t="s">
+        <v>39</v>
       </c>
       <c r="H118" s="17"/>
       <c r="I118" s="17"/>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A119" s="52"/>
+      <c r="A119" s="48"/>
       <c r="B119" s="30">
         <v>-40</v>
       </c>
-      <c r="C119" s="48" t="s">
-        <v>208</v>
-      </c>
-      <c r="D119" s="48"/>
-      <c r="E119" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F119" s="50"/>
-      <c r="G119" s="54"/>
+      <c r="C119" s="50" t="s">
+        <v>203</v>
+      </c>
+      <c r="D119" s="50"/>
+      <c r="E119" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F119" s="51"/>
+      <c r="G119" s="49"/>
       <c r="H119" s="17"/>
       <c r="I119" s="17"/>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A120" s="52"/>
+      <c r="A120" s="48"/>
       <c r="B120" s="30">
         <v>-50</v>
       </c>
-      <c r="C120" s="48" t="s">
-        <v>209</v>
-      </c>
-      <c r="D120" s="48"/>
-      <c r="E120" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F120" s="50"/>
-      <c r="G120" s="54"/>
+      <c r="C120" s="50" t="s">
+        <v>204</v>
+      </c>
+      <c r="D120" s="50"/>
+      <c r="E120" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F120" s="51"/>
+      <c r="G120" s="49"/>
       <c r="H120" s="17"/>
       <c r="I120" s="17"/>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A121" s="52"/>
+      <c r="A121" s="48"/>
       <c r="B121" s="30">
         <v>-60</v>
       </c>
-      <c r="C121" s="48" t="s">
-        <v>210</v>
-      </c>
-      <c r="D121" s="48"/>
-      <c r="E121" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F121" s="50"/>
-      <c r="G121" s="54"/>
+      <c r="C121" s="50" t="s">
+        <v>205</v>
+      </c>
+      <c r="D121" s="50"/>
+      <c r="E121" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F121" s="51"/>
+      <c r="G121" s="49"/>
       <c r="H121" s="17"/>
       <c r="I121" s="17"/>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A122" s="52"/>
+      <c r="A122" s="48"/>
       <c r="B122" s="30">
         <v>-70</v>
       </c>
-      <c r="C122" s="48" t="s">
-        <v>211</v>
-      </c>
-      <c r="D122" s="48"/>
-      <c r="E122" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F122" s="50"/>
-      <c r="G122" s="54"/>
+      <c r="C122" s="50" t="s">
+        <v>206</v>
+      </c>
+      <c r="D122" s="50"/>
+      <c r="E122" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F122" s="51"/>
+      <c r="G122" s="49"/>
       <c r="H122" s="17"/>
       <c r="I122" s="17"/>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A123" s="52"/>
+      <c r="A123" s="48"/>
       <c r="B123" s="30">
         <v>-80</v>
       </c>
-      <c r="C123" s="48" t="s">
-        <v>212</v>
-      </c>
-      <c r="D123" s="48"/>
-      <c r="E123" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F123" s="50"/>
-      <c r="G123" s="54"/>
+      <c r="C123" s="50" t="s">
+        <v>207</v>
+      </c>
+      <c r="D123" s="50"/>
+      <c r="E123" s="51" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F123" s="51"/>
+      <c r="G123" s="49"/>
       <c r="H123" s="17"/>
       <c r="I123" s="17"/>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A124" s="52"/>
+      <c r="A124" s="48"/>
       <c r="B124" s="30">
         <v>-90</v>
       </c>
-      <c r="C124" s="48" t="s">
-        <v>213</v>
-      </c>
-      <c r="D124" s="48"/>
-      <c r="E124" s="50" t="e">
+      <c r="C124" s="50" t="s">
+        <v>208</v>
+      </c>
+      <c r="D124" s="50"/>
+      <c r="E124" s="51" t="e">
         <f t="shared" ref="E124:E135" si="2">B124-C124</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F124" s="50"/>
-      <c r="G124" s="54"/>
+      <c r="F124" s="51"/>
+      <c r="G124" s="49"/>
       <c r="H124" s="17"/>
       <c r="I124" s="17"/>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A125" s="52">
+      <c r="A125" s="48">
         <v>20000</v>
       </c>
       <c r="B125" s="29">
         <v>10</v>
       </c>
-      <c r="C125" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="D125" s="48"/>
-      <c r="E125" s="50" t="e">
+      <c r="C125" s="50" t="s">
+        <v>126</v>
+      </c>
+      <c r="D125" s="50"/>
+      <c r="E125" s="51" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F125" s="50"/>
-      <c r="G125" s="54" t="s">
-        <v>12</v>
+      <c r="F125" s="51"/>
+      <c r="G125" s="49" t="s">
+        <v>11</v>
       </c>
       <c r="H125" s="17"/>
       <c r="I125" s="17"/>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A126" s="52"/>
+      <c r="A126" s="48"/>
       <c r="B126" s="29">
         <v>0</v>
       </c>
-      <c r="C126" s="48" t="s">
-        <v>132</v>
-      </c>
-      <c r="D126" s="48"/>
-      <c r="E126" s="50" t="e">
+      <c r="C126" s="50" t="s">
+        <v>127</v>
+      </c>
+      <c r="D126" s="50"/>
+      <c r="E126" s="51" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F126" s="50"/>
-      <c r="G126" s="54"/>
+      <c r="F126" s="51"/>
+      <c r="G126" s="49"/>
       <c r="H126" s="17"/>
       <c r="I126" s="17"/>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A127" s="52"/>
+      <c r="A127" s="48"/>
       <c r="B127" s="30">
         <v>-10</v>
       </c>
-      <c r="C127" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="D127" s="48"/>
-      <c r="E127" s="50" t="e">
+      <c r="C127" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="D127" s="50"/>
+      <c r="E127" s="51" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F127" s="50"/>
-      <c r="G127" s="54"/>
+      <c r="F127" s="51"/>
+      <c r="G127" s="49"/>
       <c r="H127" s="17"/>
       <c r="I127" s="17"/>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A128" s="52"/>
+      <c r="A128" s="48"/>
       <c r="B128" s="30">
         <v>-20</v>
       </c>
-      <c r="C128" s="48" t="s">
-        <v>134</v>
-      </c>
-      <c r="D128" s="48"/>
-      <c r="E128" s="50" t="e">
+      <c r="C128" s="50" t="s">
+        <v>129</v>
+      </c>
+      <c r="D128" s="50"/>
+      <c r="E128" s="51" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F128" s="50"/>
-      <c r="G128" s="54"/>
+      <c r="F128" s="51"/>
+      <c r="G128" s="49"/>
       <c r="H128" s="17"/>
       <c r="I128" s="17"/>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A129" s="52"/>
+      <c r="A129" s="48"/>
       <c r="B129" s="30">
         <v>-30</v>
       </c>
-      <c r="C129" s="48" t="s">
-        <v>135</v>
-      </c>
-      <c r="D129" s="48"/>
-      <c r="E129" s="50" t="e">
+      <c r="C129" s="50" t="s">
+        <v>130</v>
+      </c>
+      <c r="D129" s="50"/>
+      <c r="E129" s="51" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F129" s="50"/>
-      <c r="G129" s="54" t="s">
-        <v>44</v>
+      <c r="F129" s="51"/>
+      <c r="G129" s="49" t="s">
+        <v>39</v>
       </c>
       <c r="H129" s="17"/>
       <c r="I129" s="17"/>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A130" s="52"/>
+      <c r="A130" s="48"/>
       <c r="B130" s="30">
         <v>-40</v>
       </c>
-      <c r="C130" s="48" t="s">
-        <v>214</v>
-      </c>
-      <c r="D130" s="48"/>
-      <c r="E130" s="50" t="e">
+      <c r="C130" s="50" t="s">
+        <v>209</v>
+      </c>
+      <c r="D130" s="50"/>
+      <c r="E130" s="51" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F130" s="50"/>
-      <c r="G130" s="54"/>
+      <c r="F130" s="51"/>
+      <c r="G130" s="49"/>
       <c r="H130" s="17"/>
       <c r="I130" s="17"/>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A131" s="52"/>
+      <c r="A131" s="48"/>
       <c r="B131" s="30">
         <v>-50</v>
       </c>
-      <c r="C131" s="48" t="s">
-        <v>215</v>
-      </c>
-      <c r="D131" s="48"/>
-      <c r="E131" s="50" t="e">
+      <c r="C131" s="50" t="s">
+        <v>210</v>
+      </c>
+      <c r="D131" s="50"/>
+      <c r="E131" s="51" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F131" s="50"/>
-      <c r="G131" s="54"/>
+      <c r="F131" s="51"/>
+      <c r="G131" s="49"/>
       <c r="H131" s="17"/>
       <c r="I131" s="17"/>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A132" s="52"/>
+      <c r="A132" s="48"/>
       <c r="B132" s="30">
         <v>-60</v>
       </c>
-      <c r="C132" s="48" t="s">
-        <v>216</v>
-      </c>
-      <c r="D132" s="48"/>
-      <c r="E132" s="50" t="e">
+      <c r="C132" s="50" t="s">
+        <v>211</v>
+      </c>
+      <c r="D132" s="50"/>
+      <c r="E132" s="51" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F132" s="50"/>
-      <c r="G132" s="54"/>
+      <c r="F132" s="51"/>
+      <c r="G132" s="49"/>
       <c r="H132" s="17"/>
       <c r="I132" s="17"/>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A133" s="52"/>
+      <c r="A133" s="48"/>
       <c r="B133" s="30">
         <v>-70</v>
       </c>
-      <c r="C133" s="48" t="s">
-        <v>217</v>
-      </c>
-      <c r="D133" s="48"/>
-      <c r="E133" s="50" t="e">
+      <c r="C133" s="50" t="s">
+        <v>212</v>
+      </c>
+      <c r="D133" s="50"/>
+      <c r="E133" s="51" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F133" s="50"/>
-      <c r="G133" s="54"/>
+      <c r="F133" s="51"/>
+      <c r="G133" s="49"/>
       <c r="H133" s="17"/>
       <c r="I133" s="17"/>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A134" s="52"/>
+      <c r="A134" s="48"/>
       <c r="B134" s="30">
         <v>-80</v>
       </c>
-      <c r="C134" s="48" t="s">
-        <v>218</v>
-      </c>
-      <c r="D134" s="48"/>
-      <c r="E134" s="50" t="e">
+      <c r="C134" s="50" t="s">
+        <v>213</v>
+      </c>
+      <c r="D134" s="50"/>
+      <c r="E134" s="51" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F134" s="50"/>
-      <c r="G134" s="54"/>
+      <c r="F134" s="51"/>
+      <c r="G134" s="49"/>
       <c r="H134" s="17"/>
       <c r="I134" s="17"/>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A135" s="52"/>
+      <c r="A135" s="48"/>
       <c r="B135" s="30">
         <v>-90</v>
       </c>
-      <c r="C135" s="48" t="s">
-        <v>219</v>
-      </c>
-      <c r="D135" s="48"/>
-      <c r="E135" s="50" t="e">
+      <c r="C135" s="50" t="s">
+        <v>214</v>
+      </c>
+      <c r="D135" s="50"/>
+      <c r="E135" s="51" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="F135" s="50"/>
-      <c r="G135" s="54"/>
+      <c r="F135" s="51"/>
+      <c r="G135" s="49"/>
       <c r="H135" s="17"/>
       <c r="I135" s="17"/>
     </row>
@@ -3866,642 +3841,642 @@
       <c r="I136" s="17"/>
     </row>
     <row r="137" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="57" t="s">
-        <v>56</v>
-      </c>
-      <c r="B137" s="57"/>
-      <c r="C137" s="57"/>
-      <c r="D137" s="57"/>
-      <c r="E137" s="57"/>
-      <c r="F137" s="57"/>
-      <c r="G137" s="57"/>
-      <c r="H137" s="57"/>
-      <c r="I137" s="57"/>
+      <c r="A137" s="97" t="s">
+        <v>51</v>
+      </c>
+      <c r="B137" s="97"/>
+      <c r="C137" s="97"/>
+      <c r="D137" s="97"/>
+      <c r="E137" s="97"/>
+      <c r="F137" s="97"/>
+      <c r="G137" s="97"/>
+      <c r="H137" s="97"/>
+      <c r="I137" s="97"/>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A138" s="57"/>
-      <c r="B138" s="57"/>
-      <c r="C138" s="57"/>
-      <c r="D138" s="57"/>
-      <c r="E138" s="57"/>
-      <c r="F138" s="57"/>
-      <c r="G138" s="57"/>
-      <c r="H138" s="57"/>
-      <c r="I138" s="57"/>
+      <c r="A138" s="97"/>
+      <c r="B138" s="97"/>
+      <c r="C138" s="97"/>
+      <c r="D138" s="97"/>
+      <c r="E138" s="97"/>
+      <c r="F138" s="97"/>
+      <c r="G138" s="97"/>
+      <c r="H138" s="97"/>
+      <c r="I138" s="97"/>
     </row>
     <row r="139" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A139" s="31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B139" s="29" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C139" s="33" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D139" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="E139" s="52" t="s">
-        <v>54</v>
-      </c>
-      <c r="F139" s="52"/>
-      <c r="G139" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="H139" s="53"/>
+        <v>37</v>
+      </c>
+      <c r="E139" s="48" t="s">
+        <v>49</v>
+      </c>
+      <c r="F139" s="48"/>
+      <c r="G139" s="58" t="s">
+        <v>8</v>
+      </c>
+      <c r="H139" s="58"/>
       <c r="I139" s="7"/>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A140" s="52">
+      <c r="A140" s="48">
         <v>10</v>
       </c>
-      <c r="B140" s="54">
+      <c r="B140" s="49">
         <v>10</v>
       </c>
       <c r="C140" s="33" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D140" s="32">
         <v>20</v>
       </c>
-      <c r="E140" s="51" t="s">
-        <v>139</v>
-      </c>
-      <c r="F140" s="51"/>
-      <c r="G140" s="54">
+      <c r="E140" s="98" t="s">
+        <v>134</v>
+      </c>
+      <c r="F140" s="98"/>
+      <c r="G140" s="49">
         <v>-35</v>
       </c>
-      <c r="H140" s="54"/>
+      <c r="H140" s="49"/>
       <c r="I140" s="7"/>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A141" s="52"/>
-      <c r="B141" s="54"/>
+      <c r="A141" s="48"/>
+      <c r="B141" s="49"/>
       <c r="C141" s="33" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D141" s="32">
         <v>30</v>
       </c>
-      <c r="E141" s="51" t="s">
-        <v>140</v>
-      </c>
-      <c r="F141" s="51"/>
-      <c r="G141" s="54"/>
-      <c r="H141" s="54"/>
+      <c r="E141" s="98" t="s">
+        <v>135</v>
+      </c>
+      <c r="F141" s="98"/>
+      <c r="G141" s="49"/>
+      <c r="H141" s="49"/>
       <c r="I141" s="7"/>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A142" s="52">
+      <c r="A142" s="48">
         <v>1000</v>
       </c>
-      <c r="B142" s="54">
+      <c r="B142" s="49">
         <v>10</v>
       </c>
       <c r="C142" s="33" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D142" s="32">
         <v>2000</v>
       </c>
-      <c r="E142" s="51" t="s">
-        <v>141</v>
-      </c>
-      <c r="F142" s="51"/>
-      <c r="G142" s="54">
+      <c r="E142" s="98" t="s">
+        <v>136</v>
+      </c>
+      <c r="F142" s="98"/>
+      <c r="G142" s="49">
         <v>-50</v>
       </c>
-      <c r="H142" s="54"/>
+      <c r="H142" s="49"/>
       <c r="I142" s="7"/>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A143" s="52"/>
-      <c r="B143" s="54"/>
+      <c r="A143" s="48"/>
+      <c r="B143" s="49"/>
       <c r="C143" s="33" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D143" s="32">
         <v>3000</v>
       </c>
-      <c r="E143" s="51" t="s">
-        <v>142</v>
-      </c>
-      <c r="F143" s="51"/>
-      <c r="G143" s="54"/>
-      <c r="H143" s="54"/>
+      <c r="E143" s="98" t="s">
+        <v>137</v>
+      </c>
+      <c r="F143" s="98"/>
+      <c r="G143" s="49"/>
+      <c r="H143" s="49"/>
       <c r="I143" s="7"/>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A144" s="52">
+      <c r="A144" s="48">
         <v>2000</v>
       </c>
-      <c r="B144" s="54">
+      <c r="B144" s="49">
         <v>10</v>
       </c>
       <c r="C144" s="33" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D144" s="32">
         <v>4000</v>
       </c>
-      <c r="E144" s="51" t="s">
-        <v>143</v>
-      </c>
-      <c r="F144" s="51"/>
-      <c r="G144" s="54">
+      <c r="E144" s="98" t="s">
+        <v>138</v>
+      </c>
+      <c r="F144" s="98"/>
+      <c r="G144" s="49">
         <v>-50</v>
       </c>
-      <c r="H144" s="54"/>
+      <c r="H144" s="49"/>
       <c r="I144" s="7"/>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A145" s="52"/>
-      <c r="B145" s="54"/>
+      <c r="A145" s="48"/>
+      <c r="B145" s="49"/>
       <c r="C145" s="33" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D145" s="32">
         <v>6000</v>
       </c>
-      <c r="E145" s="51" t="s">
-        <v>144</v>
-      </c>
-      <c r="F145" s="51"/>
-      <c r="G145" s="54"/>
-      <c r="H145" s="54"/>
+      <c r="E145" s="98" t="s">
+        <v>139</v>
+      </c>
+      <c r="F145" s="98"/>
+      <c r="G145" s="49"/>
+      <c r="H145" s="49"/>
       <c r="I145" s="7"/>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A146" s="52"/>
-      <c r="B146" s="54"/>
+      <c r="A146" s="48"/>
+      <c r="B146" s="49"/>
       <c r="C146" s="33" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D146" s="32">
         <v>1000</v>
       </c>
-      <c r="E146" s="51" t="s">
-        <v>145</v>
-      </c>
-      <c r="F146" s="51"/>
-      <c r="G146" s="54"/>
-      <c r="H146" s="54"/>
+      <c r="E146" s="98" t="s">
+        <v>140</v>
+      </c>
+      <c r="F146" s="98"/>
+      <c r="G146" s="49"/>
+      <c r="H146" s="49"/>
       <c r="I146" s="7"/>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A147" s="52"/>
-      <c r="B147" s="54"/>
+      <c r="A147" s="48"/>
+      <c r="B147" s="49"/>
       <c r="C147" s="33" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D147" s="32">
         <v>666.6</v>
       </c>
-      <c r="E147" s="51" t="s">
-        <v>146</v>
-      </c>
-      <c r="F147" s="51"/>
-      <c r="G147" s="54"/>
-      <c r="H147" s="54"/>
+      <c r="E147" s="98" t="s">
+        <v>141</v>
+      </c>
+      <c r="F147" s="98"/>
+      <c r="G147" s="49"/>
+      <c r="H147" s="49"/>
       <c r="I147" s="7"/>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A148" s="52"/>
-      <c r="B148" s="54"/>
+      <c r="A148" s="48"/>
+      <c r="B148" s="49"/>
       <c r="C148" s="33" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D148" s="32">
         <v>3000</v>
       </c>
-      <c r="E148" s="51" t="s">
-        <v>147</v>
-      </c>
-      <c r="F148" s="51"/>
-      <c r="G148" s="54"/>
-      <c r="H148" s="54"/>
+      <c r="E148" s="98" t="s">
+        <v>142</v>
+      </c>
+      <c r="F148" s="98"/>
+      <c r="G148" s="49"/>
+      <c r="H148" s="49"/>
       <c r="I148" s="7"/>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A149" s="52"/>
-      <c r="B149" s="54"/>
+      <c r="A149" s="48"/>
+      <c r="B149" s="49"/>
       <c r="C149" s="33" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D149" s="32">
         <v>1333.3</v>
       </c>
-      <c r="E149" s="51" t="s">
-        <v>148</v>
-      </c>
-      <c r="F149" s="51"/>
-      <c r="G149" s="54"/>
-      <c r="H149" s="54"/>
+      <c r="E149" s="98" t="s">
+        <v>143</v>
+      </c>
+      <c r="F149" s="98"/>
+      <c r="G149" s="49"/>
+      <c r="H149" s="49"/>
       <c r="I149" s="7"/>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A150" s="52">
+      <c r="A150" s="48">
         <v>4000</v>
       </c>
-      <c r="B150" s="54">
+      <c r="B150" s="49">
         <v>10</v>
       </c>
       <c r="C150" s="33" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D150" s="32">
         <v>8000</v>
       </c>
-      <c r="E150" s="51" t="s">
-        <v>149</v>
-      </c>
-      <c r="F150" s="51"/>
-      <c r="G150" s="54">
+      <c r="E150" s="98" t="s">
+        <v>144</v>
+      </c>
+      <c r="F150" s="98"/>
+      <c r="G150" s="49">
         <v>-50</v>
       </c>
-      <c r="H150" s="54"/>
+      <c r="H150" s="49"/>
       <c r="I150" s="7"/>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A151" s="52"/>
-      <c r="B151" s="54"/>
+      <c r="A151" s="48"/>
+      <c r="B151" s="49"/>
       <c r="C151" s="33" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D151" s="32">
         <v>12000</v>
       </c>
-      <c r="E151" s="51" t="s">
-        <v>150</v>
-      </c>
-      <c r="F151" s="51"/>
-      <c r="G151" s="54"/>
-      <c r="H151" s="54"/>
+      <c r="E151" s="98" t="s">
+        <v>145</v>
+      </c>
+      <c r="F151" s="98"/>
+      <c r="G151" s="49"/>
+      <c r="H151" s="49"/>
       <c r="I151" s="7"/>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A152" s="52"/>
-      <c r="B152" s="54"/>
+      <c r="A152" s="48"/>
+      <c r="B152" s="49"/>
       <c r="C152" s="33" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D152" s="32">
         <v>2000</v>
       </c>
-      <c r="E152" s="51" t="s">
-        <v>151</v>
-      </c>
-      <c r="F152" s="51"/>
-      <c r="G152" s="54"/>
-      <c r="H152" s="54"/>
+      <c r="E152" s="98" t="s">
+        <v>146</v>
+      </c>
+      <c r="F152" s="98"/>
+      <c r="G152" s="49"/>
+      <c r="H152" s="49"/>
       <c r="I152" s="7"/>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A153" s="52"/>
-      <c r="B153" s="54"/>
+      <c r="A153" s="48"/>
+      <c r="B153" s="49"/>
       <c r="C153" s="33" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D153" s="32">
         <v>1333.3</v>
       </c>
-      <c r="E153" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="F153" s="51"/>
-      <c r="G153" s="54"/>
-      <c r="H153" s="54"/>
+      <c r="E153" s="98" t="s">
+        <v>147</v>
+      </c>
+      <c r="F153" s="98"/>
+      <c r="G153" s="49"/>
+      <c r="H153" s="49"/>
       <c r="I153" s="7"/>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A154" s="52"/>
-      <c r="B154" s="54"/>
+      <c r="A154" s="48"/>
+      <c r="B154" s="49"/>
       <c r="C154" s="33" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D154" s="32">
         <v>6000</v>
       </c>
-      <c r="E154" s="51" t="s">
-        <v>153</v>
-      </c>
-      <c r="F154" s="51"/>
-      <c r="G154" s="54"/>
-      <c r="H154" s="54"/>
+      <c r="E154" s="98" t="s">
+        <v>148</v>
+      </c>
+      <c r="F154" s="98"/>
+      <c r="G154" s="49"/>
+      <c r="H154" s="49"/>
       <c r="I154" s="7"/>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A155" s="52"/>
-      <c r="B155" s="54"/>
+      <c r="A155" s="48"/>
+      <c r="B155" s="49"/>
       <c r="C155" s="33" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D155" s="32">
         <v>2666.6</v>
       </c>
-      <c r="E155" s="51" t="s">
-        <v>154</v>
-      </c>
-      <c r="F155" s="51"/>
-      <c r="G155" s="54"/>
-      <c r="H155" s="54"/>
+      <c r="E155" s="98" t="s">
+        <v>149</v>
+      </c>
+      <c r="F155" s="98"/>
+      <c r="G155" s="49"/>
+      <c r="H155" s="49"/>
       <c r="I155" s="7"/>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A156" s="52">
+      <c r="A156" s="48">
         <v>8000</v>
       </c>
-      <c r="B156" s="54">
+      <c r="B156" s="49">
         <v>10</v>
       </c>
       <c r="C156" s="33" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D156" s="32">
         <v>16000</v>
       </c>
-      <c r="E156" s="51" t="s">
-        <v>155</v>
-      </c>
-      <c r="F156" s="51"/>
-      <c r="G156" s="54">
+      <c r="E156" s="98" t="s">
+        <v>150</v>
+      </c>
+      <c r="F156" s="98"/>
+      <c r="G156" s="49">
         <v>-35</v>
       </c>
-      <c r="H156" s="54"/>
+      <c r="H156" s="49"/>
       <c r="I156" s="7"/>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A157" s="52"/>
-      <c r="B157" s="54"/>
+      <c r="A157" s="48"/>
+      <c r="B157" s="49"/>
       <c r="C157" s="33" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D157" s="32">
         <v>24000</v>
       </c>
-      <c r="E157" s="51" t="s">
-        <v>156</v>
-      </c>
-      <c r="F157" s="51"/>
-      <c r="G157" s="54"/>
-      <c r="H157" s="54"/>
+      <c r="E157" s="98" t="s">
+        <v>151</v>
+      </c>
+      <c r="F157" s="98"/>
+      <c r="G157" s="49"/>
+      <c r="H157" s="49"/>
       <c r="I157" s="7"/>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A158" s="52"/>
-      <c r="B158" s="54"/>
+      <c r="A158" s="48"/>
+      <c r="B158" s="49"/>
       <c r="C158" s="33" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D158" s="32">
         <v>4000</v>
       </c>
-      <c r="E158" s="51" t="s">
-        <v>157</v>
-      </c>
-      <c r="F158" s="51"/>
-      <c r="G158" s="54">
+      <c r="E158" s="98" t="s">
+        <v>152</v>
+      </c>
+      <c r="F158" s="98"/>
+      <c r="G158" s="49">
         <v>-50</v>
       </c>
-      <c r="H158" s="54"/>
+      <c r="H158" s="49"/>
       <c r="I158" s="7"/>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A159" s="52"/>
-      <c r="B159" s="54"/>
+      <c r="A159" s="48"/>
+      <c r="B159" s="49"/>
       <c r="C159" s="33" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D159" s="32">
         <v>2666.6</v>
       </c>
-      <c r="E159" s="51" t="s">
-        <v>158</v>
-      </c>
-      <c r="F159" s="51"/>
-      <c r="G159" s="54"/>
-      <c r="H159" s="54"/>
+      <c r="E159" s="98" t="s">
+        <v>153</v>
+      </c>
+      <c r="F159" s="98"/>
+      <c r="G159" s="49"/>
+      <c r="H159" s="49"/>
       <c r="I159" s="7"/>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A160" s="52"/>
-      <c r="B160" s="54"/>
+      <c r="A160" s="48"/>
+      <c r="B160" s="49"/>
       <c r="C160" s="33" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D160" s="32">
         <v>12000</v>
       </c>
-      <c r="E160" s="51" t="s">
-        <v>159</v>
-      </c>
-      <c r="F160" s="51"/>
-      <c r="G160" s="54"/>
-      <c r="H160" s="54"/>
+      <c r="E160" s="98" t="s">
+        <v>154</v>
+      </c>
+      <c r="F160" s="98"/>
+      <c r="G160" s="49"/>
+      <c r="H160" s="49"/>
       <c r="I160" s="7"/>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A161" s="52"/>
-      <c r="B161" s="54"/>
+      <c r="A161" s="48"/>
+      <c r="B161" s="49"/>
       <c r="C161" s="33" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D161" s="32">
         <v>5333.3</v>
       </c>
-      <c r="E161" s="51" t="s">
-        <v>160</v>
-      </c>
-      <c r="F161" s="51"/>
-      <c r="G161" s="54"/>
-      <c r="H161" s="54"/>
+      <c r="E161" s="98" t="s">
+        <v>155</v>
+      </c>
+      <c r="F161" s="98"/>
+      <c r="G161" s="49"/>
+      <c r="H161" s="49"/>
       <c r="I161" s="7"/>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A162" s="52">
+      <c r="A162" s="48">
         <v>16000</v>
       </c>
-      <c r="B162" s="54">
+      <c r="B162" s="49">
         <v>10</v>
       </c>
       <c r="C162" s="33" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D162" s="32">
         <v>32000</v>
       </c>
-      <c r="E162" s="51" t="s">
-        <v>161</v>
-      </c>
-      <c r="F162" s="51"/>
-      <c r="G162" s="54">
+      <c r="E162" s="98" t="s">
+        <v>156</v>
+      </c>
+      <c r="F162" s="98"/>
+      <c r="G162" s="49">
         <v>-45</v>
       </c>
-      <c r="H162" s="54"/>
+      <c r="H162" s="49"/>
       <c r="I162" s="7"/>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A163" s="52"/>
-      <c r="B163" s="54"/>
+      <c r="A163" s="48"/>
+      <c r="B163" s="49"/>
       <c r="C163" s="33" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D163" s="32">
         <v>8000</v>
       </c>
-      <c r="E163" s="51" t="s">
-        <v>162</v>
-      </c>
-      <c r="F163" s="51"/>
-      <c r="G163" s="54">
+      <c r="E163" s="98" t="s">
+        <v>157</v>
+      </c>
+      <c r="F163" s="98"/>
+      <c r="G163" s="49">
         <v>-40</v>
       </c>
-      <c r="H163" s="54"/>
+      <c r="H163" s="49"/>
       <c r="I163" s="7"/>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A164" s="52"/>
-      <c r="B164" s="54"/>
+      <c r="A164" s="48"/>
+      <c r="B164" s="49"/>
       <c r="C164" s="33" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D164" s="32">
         <v>5333.3</v>
       </c>
-      <c r="E164" s="51" t="s">
-        <v>163</v>
-      </c>
-      <c r="F164" s="51"/>
-      <c r="G164" s="54"/>
-      <c r="H164" s="54"/>
+      <c r="E164" s="98" t="s">
+        <v>158</v>
+      </c>
+      <c r="F164" s="98"/>
+      <c r="G164" s="49"/>
+      <c r="H164" s="49"/>
       <c r="I164" s="7"/>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A165" s="52"/>
-      <c r="B165" s="54"/>
+      <c r="A165" s="48"/>
+      <c r="B165" s="49"/>
       <c r="C165" s="33" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D165" s="32">
         <v>24000</v>
       </c>
-      <c r="E165" s="51" t="s">
-        <v>164</v>
-      </c>
-      <c r="F165" s="51"/>
-      <c r="G165" s="54"/>
-      <c r="H165" s="54"/>
+      <c r="E165" s="98" t="s">
+        <v>159</v>
+      </c>
+      <c r="F165" s="98"/>
+      <c r="G165" s="49"/>
+      <c r="H165" s="49"/>
       <c r="I165" s="7"/>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A166" s="52"/>
-      <c r="B166" s="54"/>
+      <c r="A166" s="48"/>
+      <c r="B166" s="49"/>
       <c r="C166" s="33" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D166" s="32">
         <v>10666.6</v>
       </c>
-      <c r="E166" s="51" t="s">
-        <v>165</v>
-      </c>
-      <c r="F166" s="51"/>
-      <c r="G166" s="54"/>
-      <c r="H166" s="54"/>
+      <c r="E166" s="98" t="s">
+        <v>160</v>
+      </c>
+      <c r="F166" s="98"/>
+      <c r="G166" s="49"/>
+      <c r="H166" s="49"/>
       <c r="I166" s="7"/>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A167" s="52">
+      <c r="A167" s="48">
         <v>20000</v>
       </c>
-      <c r="B167" s="54">
+      <c r="B167" s="49">
         <v>10</v>
       </c>
       <c r="C167" s="33" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D167" s="32">
         <v>40000</v>
       </c>
-      <c r="E167" s="51" t="s">
-        <v>166</v>
-      </c>
-      <c r="F167" s="51"/>
-      <c r="G167" s="54">
+      <c r="E167" s="98" t="s">
+        <v>161</v>
+      </c>
+      <c r="F167" s="98"/>
+      <c r="G167" s="49">
         <v>-45</v>
       </c>
-      <c r="H167" s="54"/>
+      <c r="H167" s="49"/>
       <c r="I167" s="7"/>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A168" s="52"/>
-      <c r="B168" s="54"/>
+      <c r="A168" s="48"/>
+      <c r="B168" s="49"/>
       <c r="C168" s="33" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D168" s="32">
         <v>10000</v>
       </c>
-      <c r="E168" s="51" t="s">
-        <v>167</v>
-      </c>
-      <c r="F168" s="51"/>
-      <c r="G168" s="54">
+      <c r="E168" s="98" t="s">
+        <v>162</v>
+      </c>
+      <c r="F168" s="98"/>
+      <c r="G168" s="49">
         <v>-40</v>
       </c>
-      <c r="H168" s="54"/>
+      <c r="H168" s="49"/>
       <c r="I168" s="7"/>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A169" s="52"/>
-      <c r="B169" s="54"/>
+      <c r="A169" s="48"/>
+      <c r="B169" s="49"/>
       <c r="C169" s="33" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="D169" s="32">
         <v>6666.6</v>
       </c>
-      <c r="E169" s="51" t="s">
-        <v>168</v>
-      </c>
-      <c r="F169" s="51"/>
-      <c r="G169" s="54"/>
-      <c r="H169" s="54"/>
+      <c r="E169" s="98" t="s">
+        <v>163</v>
+      </c>
+      <c r="F169" s="98"/>
+      <c r="G169" s="49"/>
+      <c r="H169" s="49"/>
       <c r="I169" s="7"/>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A170" s="52"/>
-      <c r="B170" s="54"/>
+      <c r="A170" s="48"/>
+      <c r="B170" s="49"/>
       <c r="C170" s="33" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D170" s="32">
         <v>30000</v>
       </c>
-      <c r="E170" s="51" t="s">
-        <v>169</v>
-      </c>
-      <c r="F170" s="51"/>
-      <c r="G170" s="54"/>
-      <c r="H170" s="54"/>
+      <c r="E170" s="98" t="s">
+        <v>164</v>
+      </c>
+      <c r="F170" s="98"/>
+      <c r="G170" s="49"/>
+      <c r="H170" s="49"/>
       <c r="I170" s="7"/>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A171" s="52"/>
-      <c r="B171" s="54"/>
+      <c r="A171" s="48"/>
+      <c r="B171" s="49"/>
       <c r="C171" s="33" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D171" s="32">
         <v>13333.3</v>
       </c>
-      <c r="E171" s="51" t="s">
-        <v>170</v>
-      </c>
-      <c r="F171" s="51"/>
-      <c r="G171" s="54"/>
-      <c r="H171" s="54"/>
+      <c r="E171" s="98" t="s">
+        <v>165</v>
+      </c>
+      <c r="F171" s="98"/>
+      <c r="G171" s="49"/>
+      <c r="H171" s="49"/>
       <c r="I171" s="7"/>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.25">
@@ -4517,22 +4492,22 @@
     </row>
     <row r="173" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A173" s="31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B173" s="29" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C173" s="33" t="s">
-        <v>47</v>
-      </c>
-      <c r="D173" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="E173" s="53"/>
-      <c r="F173" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="G173" s="53"/>
+        <v>42</v>
+      </c>
+      <c r="D173" s="58" t="s">
+        <v>57</v>
+      </c>
+      <c r="E173" s="58"/>
+      <c r="F173" s="58" t="s">
+        <v>8</v>
+      </c>
+      <c r="G173" s="58"/>
       <c r="H173" s="17"/>
       <c r="I173" s="7"/>
       <c r="J173"/>
@@ -4541,20 +4516,20 @@
       <c r="A174" s="29">
         <v>10</v>
       </c>
-      <c r="B174" s="54">
+      <c r="B174" s="49">
         <v>10</v>
       </c>
-      <c r="C174" s="49" t="s">
-        <v>55</v>
-      </c>
-      <c r="D174" s="55" t="s">
-        <v>171</v>
-      </c>
-      <c r="E174" s="55"/>
-      <c r="F174" s="54">
+      <c r="C174" s="99" t="s">
+        <v>50</v>
+      </c>
+      <c r="D174" s="100" t="s">
+        <v>166</v>
+      </c>
+      <c r="E174" s="100"/>
+      <c r="F174" s="49">
         <v>-50</v>
       </c>
-      <c r="G174" s="54"/>
+      <c r="G174" s="49"/>
       <c r="H174" s="17"/>
       <c r="I174" s="17"/>
     </row>
@@ -4562,16 +4537,16 @@
       <c r="A175" s="29">
         <v>1000</v>
       </c>
-      <c r="B175" s="54"/>
-      <c r="C175" s="49"/>
-      <c r="D175" s="55" t="s">
-        <v>172</v>
-      </c>
-      <c r="E175" s="55"/>
-      <c r="F175" s="54">
+      <c r="B175" s="49"/>
+      <c r="C175" s="99"/>
+      <c r="D175" s="100" t="s">
+        <v>167</v>
+      </c>
+      <c r="E175" s="100"/>
+      <c r="F175" s="49">
         <v>-65</v>
       </c>
-      <c r="G175" s="54"/>
+      <c r="G175" s="49"/>
       <c r="H175" s="17"/>
       <c r="I175" s="17"/>
     </row>
@@ -4579,16 +4554,16 @@
       <c r="A176" s="29">
         <v>2000</v>
       </c>
-      <c r="B176" s="54"/>
-      <c r="C176" s="49"/>
-      <c r="D176" s="55" t="s">
-        <v>173</v>
-      </c>
-      <c r="E176" s="55"/>
-      <c r="F176" s="54">
+      <c r="B176" s="49"/>
+      <c r="C176" s="99"/>
+      <c r="D176" s="100" t="s">
+        <v>168</v>
+      </c>
+      <c r="E176" s="100"/>
+      <c r="F176" s="49">
         <v>-60</v>
       </c>
-      <c r="G176" s="54"/>
+      <c r="G176" s="49"/>
       <c r="H176" s="17"/>
       <c r="I176" s="17"/>
     </row>
@@ -4596,16 +4571,16 @@
       <c r="A177" s="29">
         <v>4000</v>
       </c>
-      <c r="B177" s="54"/>
-      <c r="C177" s="49"/>
-      <c r="D177" s="55" t="s">
-        <v>174</v>
-      </c>
-      <c r="E177" s="55"/>
-      <c r="F177" s="54">
+      <c r="B177" s="49"/>
+      <c r="C177" s="99"/>
+      <c r="D177" s="100" t="s">
+        <v>169</v>
+      </c>
+      <c r="E177" s="100"/>
+      <c r="F177" s="49">
         <v>-60</v>
       </c>
-      <c r="G177" s="54"/>
+      <c r="G177" s="49"/>
       <c r="H177" s="17"/>
       <c r="I177" s="17"/>
     </row>
@@ -4613,16 +4588,16 @@
       <c r="A178" s="29">
         <v>8000</v>
       </c>
-      <c r="B178" s="54"/>
-      <c r="C178" s="49"/>
-      <c r="D178" s="55" t="s">
-        <v>175</v>
-      </c>
-      <c r="E178" s="55"/>
-      <c r="F178" s="54">
+      <c r="B178" s="49"/>
+      <c r="C178" s="99"/>
+      <c r="D178" s="100" t="s">
+        <v>170</v>
+      </c>
+      <c r="E178" s="100"/>
+      <c r="F178" s="49">
         <v>-50</v>
       </c>
-      <c r="G178" s="54"/>
+      <c r="G178" s="49"/>
       <c r="H178" s="17"/>
       <c r="I178" s="17"/>
     </row>
@@ -4630,16 +4605,16 @@
       <c r="A179" s="29">
         <v>16000</v>
       </c>
-      <c r="B179" s="54"/>
-      <c r="C179" s="49"/>
-      <c r="D179" s="55" t="s">
-        <v>176</v>
-      </c>
-      <c r="E179" s="55"/>
-      <c r="F179" s="54">
+      <c r="B179" s="49"/>
+      <c r="C179" s="99"/>
+      <c r="D179" s="100" t="s">
+        <v>171</v>
+      </c>
+      <c r="E179" s="100"/>
+      <c r="F179" s="49">
         <v>-45</v>
       </c>
-      <c r="G179" s="54"/>
+      <c r="G179" s="49"/>
       <c r="H179" s="17"/>
       <c r="I179" s="17"/>
     </row>
@@ -4647,16 +4622,16 @@
       <c r="A180" s="29">
         <v>20000</v>
       </c>
-      <c r="B180" s="54"/>
-      <c r="C180" s="49"/>
-      <c r="D180" s="55" t="s">
-        <v>177</v>
-      </c>
-      <c r="E180" s="55"/>
-      <c r="F180" s="54">
+      <c r="B180" s="49"/>
+      <c r="C180" s="99"/>
+      <c r="D180" s="100" t="s">
+        <v>172</v>
+      </c>
+      <c r="E180" s="100"/>
+      <c r="F180" s="49">
         <v>-45</v>
       </c>
-      <c r="G180" s="54"/>
+      <c r="G180" s="49"/>
       <c r="H180" s="17"/>
       <c r="I180" s="17"/>
     </row>
@@ -4673,7 +4648,7 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B182" s="11"/>
       <c r="C182" s="15"/>
@@ -4686,19 +4661,19 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="29" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B183" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="C183" s="49" t="s">
-        <v>61</v>
-      </c>
-      <c r="D183" s="49"/>
-      <c r="E183" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="F183" s="53"/>
+        <v>54</v>
+      </c>
+      <c r="C183" s="99" t="s">
+        <v>56</v>
+      </c>
+      <c r="D183" s="99"/>
+      <c r="E183" s="58" t="s">
+        <v>55</v>
+      </c>
+      <c r="F183" s="58"/>
       <c r="G183" s="17"/>
       <c r="H183" s="17"/>
       <c r="I183" s="17"/>
@@ -4710,14 +4685,14 @@
       <c r="B184" s="30">
         <v>10</v>
       </c>
-      <c r="C184" s="48">
+      <c r="C184" s="50">
         <v>1.36</v>
       </c>
-      <c r="D184" s="48"/>
-      <c r="E184" s="49">
+      <c r="D184" s="50"/>
+      <c r="E184" s="99">
         <v>1.7</v>
       </c>
-      <c r="F184" s="49"/>
+      <c r="F184" s="99"/>
       <c r="G184" s="17"/>
       <c r="H184" s="17"/>
       <c r="I184" s="17"/>
@@ -4729,12 +4704,12 @@
       <c r="B185" s="30">
         <v>20</v>
       </c>
-      <c r="C185" s="48">
+      <c r="C185" s="50">
         <v>1.36</v>
       </c>
-      <c r="D185" s="48"/>
-      <c r="E185" s="49"/>
-      <c r="F185" s="49"/>
+      <c r="D185" s="50"/>
+      <c r="E185" s="99"/>
+      <c r="F185" s="99"/>
       <c r="G185" s="17"/>
       <c r="H185" s="17"/>
       <c r="I185" s="17"/>
@@ -4746,12 +4721,12 @@
       <c r="B186" s="30">
         <v>30</v>
       </c>
-      <c r="C186" s="48">
+      <c r="C186" s="50">
         <v>1.32</v>
       </c>
-      <c r="D186" s="48"/>
-      <c r="E186" s="49"/>
-      <c r="F186" s="49"/>
+      <c r="D186" s="50"/>
+      <c r="E186" s="99"/>
+      <c r="F186" s="99"/>
       <c r="G186" s="17"/>
       <c r="H186" s="17"/>
       <c r="I186" s="17"/>
@@ -4763,12 +4738,12 @@
       <c r="B187" s="30">
         <v>40</v>
       </c>
-      <c r="C187" s="48">
+      <c r="C187" s="50">
         <v>1.27</v>
       </c>
-      <c r="D187" s="48"/>
-      <c r="E187" s="49"/>
-      <c r="F187" s="49"/>
+      <c r="D187" s="50"/>
+      <c r="E187" s="99"/>
+      <c r="F187" s="99"/>
       <c r="G187" s="17"/>
       <c r="H187" s="17"/>
       <c r="I187" s="17"/>
@@ -4780,12 +4755,12 @@
       <c r="B188" s="30">
         <v>50</v>
       </c>
-      <c r="C188" s="48">
+      <c r="C188" s="50">
         <v>1.31</v>
       </c>
-      <c r="D188" s="48"/>
-      <c r="E188" s="49"/>
-      <c r="F188" s="49"/>
+      <c r="D188" s="50"/>
+      <c r="E188" s="99"/>
+      <c r="F188" s="99"/>
       <c r="G188" s="17"/>
       <c r="H188" s="17"/>
       <c r="I188" s="17"/>
@@ -4797,12 +4772,12 @@
       <c r="B189" s="30">
         <v>60</v>
       </c>
-      <c r="C189" s="48">
+      <c r="C189" s="50">
         <v>1.36</v>
       </c>
-      <c r="D189" s="48"/>
-      <c r="E189" s="49"/>
-      <c r="F189" s="49"/>
+      <c r="D189" s="50"/>
+      <c r="E189" s="99"/>
+      <c r="F189" s="99"/>
       <c r="G189" s="17"/>
       <c r="H189" s="17"/>
       <c r="I189" s="17"/>
@@ -4814,12 +4789,12 @@
       <c r="B190" s="30">
         <v>70</v>
       </c>
-      <c r="C190" s="48">
+      <c r="C190" s="50">
         <v>1.3260000000000001</v>
       </c>
-      <c r="D190" s="48"/>
-      <c r="E190" s="49"/>
-      <c r="F190" s="49"/>
+      <c r="D190" s="50"/>
+      <c r="E190" s="99"/>
+      <c r="F190" s="99"/>
       <c r="G190" s="17"/>
       <c r="H190" s="17"/>
       <c r="I190" s="17"/>
@@ -4831,12 +4806,12 @@
       <c r="B191" s="30">
         <v>80</v>
       </c>
-      <c r="C191" s="48">
+      <c r="C191" s="50">
         <v>1.28</v>
       </c>
-      <c r="D191" s="48"/>
-      <c r="E191" s="49"/>
-      <c r="F191" s="49"/>
+      <c r="D191" s="50"/>
+      <c r="E191" s="99"/>
+      <c r="F191" s="99"/>
       <c r="G191" s="17"/>
       <c r="H191" s="17"/>
       <c r="I191" s="17"/>
@@ -4848,12 +4823,12 @@
       <c r="B192" s="30">
         <v>90</v>
       </c>
-      <c r="C192" s="48">
+      <c r="C192" s="50">
         <v>1.32</v>
       </c>
-      <c r="D192" s="48"/>
-      <c r="E192" s="49"/>
-      <c r="F192" s="49"/>
+      <c r="D192" s="50"/>
+      <c r="E192" s="99"/>
+      <c r="F192" s="99"/>
       <c r="G192" s="17"/>
       <c r="H192" s="17"/>
       <c r="I192" s="17"/>
@@ -4865,12 +4840,12 @@
       <c r="B193" s="30">
         <v>100</v>
       </c>
-      <c r="C193" s="48">
+      <c r="C193" s="50">
         <v>1.28</v>
       </c>
-      <c r="D193" s="48"/>
-      <c r="E193" s="49"/>
-      <c r="F193" s="49"/>
+      <c r="D193" s="50"/>
+      <c r="E193" s="99"/>
+      <c r="F193" s="99"/>
       <c r="G193" s="17"/>
       <c r="H193" s="17"/>
       <c r="I193" s="17"/>
@@ -4882,21 +4857,21 @@
       <c r="B194" s="30">
         <v>110</v>
       </c>
-      <c r="C194" s="48">
+      <c r="C194" s="50">
         <v>1.32</v>
       </c>
-      <c r="D194" s="48"/>
-      <c r="E194" s="49"/>
-      <c r="F194" s="49"/>
+      <c r="D194" s="50"/>
+      <c r="E194" s="99"/>
+      <c r="F194" s="99"/>
       <c r="G194" s="17"/>
       <c r="H194" s="17"/>
       <c r="I194" s="17"/>
     </row>
     <row r="196" spans="1:9" s="45" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="95" t="s">
-        <v>85</v>
-      </c>
-      <c r="B196" s="95"/>
+      <c r="A196" s="52" t="s">
+        <v>80</v>
+      </c>
+      <c r="B196" s="52"/>
       <c r="C196" s="41"/>
       <c r="D196" s="42"/>
       <c r="E196" s="43"/>
@@ -4905,32 +4880,32 @@
       <c r="H196" s="9"/>
     </row>
     <row r="197" spans="1:9" s="45" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="95" t="s">
-        <v>86</v>
-      </c>
-      <c r="B197" s="95"/>
+      <c r="A197" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="B197" s="52"/>
       <c r="C197" s="42"/>
       <c r="D197" s="46" t="s">
-        <v>87</v>
-      </c>
-      <c r="E197" s="96" t="s">
-        <v>88</v>
-      </c>
-      <c r="F197" s="97"/>
+        <v>82</v>
+      </c>
+      <c r="E197" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="F197" s="54"/>
       <c r="G197" s="43" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H197" s="47"/>
     </row>
     <row r="198" spans="1:9" s="45" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A198" s="95" t="s">
-        <v>10</v>
-      </c>
-      <c r="B198" s="95"/>
-      <c r="C198" s="98" t="s">
-        <v>90</v>
-      </c>
-      <c r="D198" s="98"/>
+      <c r="A198" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="B198" s="52"/>
+      <c r="C198" s="55" t="s">
+        <v>85</v>
+      </c>
+      <c r="D198" s="55"/>
       <c r="E198" s="9"/>
       <c r="F198" s="9"/>
       <c r="G198" s="9"/>
@@ -4938,86 +4913,259 @@
     </row>
   </sheetData>
   <mergeCells count="367">
-    <mergeCell ref="A70:A80"/>
-    <mergeCell ref="G70:G73"/>
-    <mergeCell ref="G74:G80"/>
-    <mergeCell ref="A81:A91"/>
-    <mergeCell ref="G81:G84"/>
-    <mergeCell ref="G85:G91"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="E81:F81"/>
-    <mergeCell ref="E82:F82"/>
-    <mergeCell ref="A196:B196"/>
-    <mergeCell ref="A197:B197"/>
-    <mergeCell ref="E197:F197"/>
-    <mergeCell ref="A198:B198"/>
-    <mergeCell ref="C198:D198"/>
-    <mergeCell ref="C191:D191"/>
-    <mergeCell ref="C192:D192"/>
-    <mergeCell ref="C193:D193"/>
-    <mergeCell ref="C194:D194"/>
-    <mergeCell ref="E83:F83"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A7:I7"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="G20:H21"/>
-    <mergeCell ref="E20:F21"/>
-    <mergeCell ref="A20:D21"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="A37:I37"/>
-    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="C189:D189"/>
+    <mergeCell ref="C190:D190"/>
+    <mergeCell ref="E184:F194"/>
+    <mergeCell ref="C184:D184"/>
+    <mergeCell ref="C185:D185"/>
+    <mergeCell ref="C186:D186"/>
+    <mergeCell ref="C187:D187"/>
+    <mergeCell ref="C188:D188"/>
+    <mergeCell ref="E129:F129"/>
+    <mergeCell ref="E130:F130"/>
+    <mergeCell ref="E131:F131"/>
+    <mergeCell ref="E132:F132"/>
+    <mergeCell ref="E133:F133"/>
+    <mergeCell ref="E134:F134"/>
+    <mergeCell ref="E135:F135"/>
+    <mergeCell ref="C134:D134"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="C131:D131"/>
+    <mergeCell ref="C132:D132"/>
+    <mergeCell ref="C133:D133"/>
+    <mergeCell ref="E165:F165"/>
+    <mergeCell ref="E166:F166"/>
+    <mergeCell ref="E167:F167"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="C183:D183"/>
+    <mergeCell ref="E183:F183"/>
+    <mergeCell ref="E120:F120"/>
+    <mergeCell ref="E121:F121"/>
+    <mergeCell ref="E122:F122"/>
+    <mergeCell ref="E123:F123"/>
+    <mergeCell ref="E124:F124"/>
+    <mergeCell ref="E125:F125"/>
+    <mergeCell ref="E126:F126"/>
+    <mergeCell ref="E127:F127"/>
+    <mergeCell ref="E128:F128"/>
+    <mergeCell ref="E111:F111"/>
+    <mergeCell ref="E112:F112"/>
+    <mergeCell ref="E113:F113"/>
+    <mergeCell ref="E114:F114"/>
+    <mergeCell ref="E115:F115"/>
+    <mergeCell ref="E116:F116"/>
+    <mergeCell ref="E117:F117"/>
+    <mergeCell ref="E118:F118"/>
+    <mergeCell ref="E119:F119"/>
+    <mergeCell ref="E102:F102"/>
+    <mergeCell ref="E103:F103"/>
+    <mergeCell ref="E104:F104"/>
+    <mergeCell ref="E105:F105"/>
+    <mergeCell ref="E106:F106"/>
+    <mergeCell ref="E107:F107"/>
+    <mergeCell ref="E109:F109"/>
+    <mergeCell ref="E110:F110"/>
+    <mergeCell ref="E93:F93"/>
+    <mergeCell ref="E94:F94"/>
+    <mergeCell ref="E95:F95"/>
+    <mergeCell ref="E96:F96"/>
+    <mergeCell ref="E97:F97"/>
+    <mergeCell ref="E98:F98"/>
+    <mergeCell ref="E99:F99"/>
+    <mergeCell ref="E100:F100"/>
+    <mergeCell ref="E101:F101"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="E88:F88"/>
+    <mergeCell ref="E89:F89"/>
+    <mergeCell ref="E90:F90"/>
+    <mergeCell ref="E91:F91"/>
+    <mergeCell ref="E92:F92"/>
+    <mergeCell ref="E86:F86"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="E80:F80"/>
+    <mergeCell ref="C125:D125"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="C127:D127"/>
+    <mergeCell ref="C128:D128"/>
+    <mergeCell ref="C129:D129"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="C118:D118"/>
+    <mergeCell ref="C119:D119"/>
+    <mergeCell ref="C120:D120"/>
+    <mergeCell ref="C121:D121"/>
+    <mergeCell ref="C122:D122"/>
+    <mergeCell ref="C123:D123"/>
+    <mergeCell ref="C124:D124"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="E84:F84"/>
+    <mergeCell ref="E85:F85"/>
+    <mergeCell ref="E140:F140"/>
+    <mergeCell ref="E149:F149"/>
+    <mergeCell ref="B174:B180"/>
+    <mergeCell ref="C174:C180"/>
+    <mergeCell ref="D174:E174"/>
+    <mergeCell ref="D173:E173"/>
+    <mergeCell ref="F173:G173"/>
+    <mergeCell ref="F174:G174"/>
+    <mergeCell ref="D175:E175"/>
+    <mergeCell ref="F175:G175"/>
+    <mergeCell ref="D176:E176"/>
+    <mergeCell ref="F176:G176"/>
+    <mergeCell ref="D177:E177"/>
+    <mergeCell ref="F177:G177"/>
+    <mergeCell ref="D178:E178"/>
+    <mergeCell ref="F178:G178"/>
+    <mergeCell ref="D179:E179"/>
+    <mergeCell ref="F179:G179"/>
+    <mergeCell ref="D180:E180"/>
+    <mergeCell ref="E159:F159"/>
+    <mergeCell ref="E160:F160"/>
+    <mergeCell ref="E161:F161"/>
+    <mergeCell ref="E162:F162"/>
+    <mergeCell ref="F180:G180"/>
+    <mergeCell ref="E168:F168"/>
+    <mergeCell ref="E169:F169"/>
+    <mergeCell ref="E170:F170"/>
+    <mergeCell ref="E171:F171"/>
+    <mergeCell ref="A162:A166"/>
+    <mergeCell ref="B162:B166"/>
+    <mergeCell ref="A167:A171"/>
+    <mergeCell ref="B167:B171"/>
+    <mergeCell ref="E163:F163"/>
+    <mergeCell ref="E164:F164"/>
+    <mergeCell ref="G142:H143"/>
+    <mergeCell ref="G144:H149"/>
+    <mergeCell ref="G150:H155"/>
+    <mergeCell ref="G156:H157"/>
+    <mergeCell ref="G158:H161"/>
+    <mergeCell ref="G162:H162"/>
+    <mergeCell ref="G163:H166"/>
+    <mergeCell ref="G167:H167"/>
+    <mergeCell ref="G168:H171"/>
+    <mergeCell ref="E146:F146"/>
+    <mergeCell ref="A150:A155"/>
+    <mergeCell ref="B150:B155"/>
+    <mergeCell ref="A156:A161"/>
+    <mergeCell ref="B156:B161"/>
+    <mergeCell ref="A142:A143"/>
+    <mergeCell ref="B142:B143"/>
+    <mergeCell ref="B144:B149"/>
+    <mergeCell ref="A144:A149"/>
+    <mergeCell ref="E147:F147"/>
+    <mergeCell ref="E148:F148"/>
+    <mergeCell ref="E145:F145"/>
+    <mergeCell ref="E144:F144"/>
+    <mergeCell ref="E143:F143"/>
+    <mergeCell ref="E142:F142"/>
+    <mergeCell ref="E150:F150"/>
+    <mergeCell ref="E151:F151"/>
+    <mergeCell ref="E152:F152"/>
+    <mergeCell ref="E153:F153"/>
+    <mergeCell ref="E154:F154"/>
+    <mergeCell ref="E155:F155"/>
+    <mergeCell ref="E156:F156"/>
+    <mergeCell ref="E157:F157"/>
+    <mergeCell ref="E158:F158"/>
+    <mergeCell ref="A125:A135"/>
+    <mergeCell ref="G125:G128"/>
+    <mergeCell ref="G129:G135"/>
+    <mergeCell ref="A42:I43"/>
+    <mergeCell ref="A137:I138"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="A140:A141"/>
+    <mergeCell ref="G139:H139"/>
+    <mergeCell ref="G140:H141"/>
+    <mergeCell ref="E139:F139"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="A92:A102"/>
+    <mergeCell ref="G92:G95"/>
+    <mergeCell ref="G96:G102"/>
+    <mergeCell ref="A103:A113"/>
+    <mergeCell ref="E141:F141"/>
+    <mergeCell ref="G103:G106"/>
+    <mergeCell ref="G107:G113"/>
+    <mergeCell ref="A114:A124"/>
+    <mergeCell ref="G114:G117"/>
+    <mergeCell ref="G118:G124"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="C105:D105"/>
+    <mergeCell ref="C106:D106"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="C115:D115"/>
+    <mergeCell ref="E108:F108"/>
+    <mergeCell ref="A59:A69"/>
+    <mergeCell ref="G59:G62"/>
+    <mergeCell ref="G63:G69"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="A56:I57"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="C44:D44"/>
     <mergeCell ref="E44:F44"/>
@@ -5042,148 +5190,86 @@
     <mergeCell ref="C47:D47"/>
     <mergeCell ref="C48:D48"/>
     <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="A56:I57"/>
-    <mergeCell ref="A59:A69"/>
-    <mergeCell ref="G59:G62"/>
-    <mergeCell ref="G63:G69"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C66:D66"/>
-    <mergeCell ref="C67:D67"/>
-    <mergeCell ref="C68:D68"/>
-    <mergeCell ref="G103:G106"/>
-    <mergeCell ref="G107:G113"/>
-    <mergeCell ref="A114:A124"/>
-    <mergeCell ref="G114:G117"/>
-    <mergeCell ref="G118:G124"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="C105:D105"/>
-    <mergeCell ref="C106:D106"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="C115:D115"/>
-    <mergeCell ref="E108:F108"/>
-    <mergeCell ref="A125:A135"/>
-    <mergeCell ref="G125:G128"/>
-    <mergeCell ref="G129:G135"/>
-    <mergeCell ref="A42:I43"/>
-    <mergeCell ref="A137:I138"/>
-    <mergeCell ref="B140:B141"/>
-    <mergeCell ref="A140:A141"/>
-    <mergeCell ref="G139:H139"/>
-    <mergeCell ref="G140:H141"/>
-    <mergeCell ref="E139:F139"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="A92:A102"/>
-    <mergeCell ref="G92:G95"/>
-    <mergeCell ref="G96:G102"/>
-    <mergeCell ref="A103:A113"/>
-    <mergeCell ref="E141:F141"/>
-    <mergeCell ref="E146:F146"/>
-    <mergeCell ref="A150:A155"/>
-    <mergeCell ref="B150:B155"/>
-    <mergeCell ref="A156:A161"/>
-    <mergeCell ref="B156:B161"/>
-    <mergeCell ref="A142:A143"/>
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="B144:B149"/>
-    <mergeCell ref="A144:A149"/>
-    <mergeCell ref="E147:F147"/>
-    <mergeCell ref="E148:F148"/>
-    <mergeCell ref="E145:F145"/>
-    <mergeCell ref="E144:F144"/>
-    <mergeCell ref="E143:F143"/>
-    <mergeCell ref="E142:F142"/>
-    <mergeCell ref="E150:F150"/>
-    <mergeCell ref="E151:F151"/>
-    <mergeCell ref="E152:F152"/>
-    <mergeCell ref="E153:F153"/>
-    <mergeCell ref="E154:F154"/>
-    <mergeCell ref="E155:F155"/>
-    <mergeCell ref="E156:F156"/>
-    <mergeCell ref="E157:F157"/>
-    <mergeCell ref="E158:F158"/>
-    <mergeCell ref="G142:H143"/>
-    <mergeCell ref="G144:H149"/>
-    <mergeCell ref="G150:H155"/>
-    <mergeCell ref="G156:H157"/>
-    <mergeCell ref="G158:H161"/>
-    <mergeCell ref="G162:H162"/>
-    <mergeCell ref="G163:H166"/>
-    <mergeCell ref="G167:H167"/>
-    <mergeCell ref="G168:H171"/>
-    <mergeCell ref="E168:F168"/>
-    <mergeCell ref="E169:F169"/>
-    <mergeCell ref="E170:F170"/>
-    <mergeCell ref="E171:F171"/>
-    <mergeCell ref="A162:A166"/>
-    <mergeCell ref="B162:B166"/>
-    <mergeCell ref="A167:A171"/>
-    <mergeCell ref="B167:B171"/>
-    <mergeCell ref="E163:F163"/>
-    <mergeCell ref="E164:F164"/>
-    <mergeCell ref="E140:F140"/>
-    <mergeCell ref="E149:F149"/>
-    <mergeCell ref="B174:B180"/>
-    <mergeCell ref="C174:C180"/>
-    <mergeCell ref="D174:E174"/>
-    <mergeCell ref="D173:E173"/>
-    <mergeCell ref="F173:G173"/>
-    <mergeCell ref="F174:G174"/>
-    <mergeCell ref="D175:E175"/>
-    <mergeCell ref="F175:G175"/>
-    <mergeCell ref="D176:E176"/>
-    <mergeCell ref="F176:G176"/>
-    <mergeCell ref="D177:E177"/>
-    <mergeCell ref="F177:G177"/>
-    <mergeCell ref="D178:E178"/>
-    <mergeCell ref="F178:G178"/>
-    <mergeCell ref="D179:E179"/>
-    <mergeCell ref="F179:G179"/>
-    <mergeCell ref="D180:E180"/>
-    <mergeCell ref="E159:F159"/>
-    <mergeCell ref="E160:F160"/>
-    <mergeCell ref="E161:F161"/>
-    <mergeCell ref="E162:F162"/>
-    <mergeCell ref="F180:G180"/>
-    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="G20:H21"/>
+    <mergeCell ref="E20:F21"/>
+    <mergeCell ref="A20:D21"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A196:B196"/>
+    <mergeCell ref="A197:B197"/>
+    <mergeCell ref="E197:F197"/>
+    <mergeCell ref="A198:B198"/>
+    <mergeCell ref="C198:D198"/>
+    <mergeCell ref="C191:D191"/>
+    <mergeCell ref="C192:D192"/>
+    <mergeCell ref="C193:D193"/>
+    <mergeCell ref="C194:D194"/>
+    <mergeCell ref="A70:A80"/>
+    <mergeCell ref="G70:G73"/>
+    <mergeCell ref="G74:G80"/>
+    <mergeCell ref="A81:A91"/>
+    <mergeCell ref="G81:G84"/>
+    <mergeCell ref="G85:G91"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="E81:F81"/>
+    <mergeCell ref="E82:F82"/>
+    <mergeCell ref="E83:F83"/>
     <mergeCell ref="C70:D70"/>
     <mergeCell ref="C71:D71"/>
     <mergeCell ref="C72:D72"/>
@@ -5194,117 +5280,6 @@
     <mergeCell ref="E79:F79"/>
     <mergeCell ref="C75:D75"/>
     <mergeCell ref="C76:D76"/>
-    <mergeCell ref="C77:D77"/>
-    <mergeCell ref="E80:F80"/>
-    <mergeCell ref="C125:D125"/>
-    <mergeCell ref="C126:D126"/>
-    <mergeCell ref="C127:D127"/>
-    <mergeCell ref="C128:D128"/>
-    <mergeCell ref="C129:D129"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="C117:D117"/>
-    <mergeCell ref="C118:D118"/>
-    <mergeCell ref="C119:D119"/>
-    <mergeCell ref="C120:D120"/>
-    <mergeCell ref="C121:D121"/>
-    <mergeCell ref="C122:D122"/>
-    <mergeCell ref="C123:D123"/>
-    <mergeCell ref="C124:D124"/>
-    <mergeCell ref="C107:D107"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="E84:F84"/>
-    <mergeCell ref="E85:F85"/>
-    <mergeCell ref="E86:F86"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="E76:F76"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="E87:F87"/>
-    <mergeCell ref="E88:F88"/>
-    <mergeCell ref="E89:F89"/>
-    <mergeCell ref="E90:F90"/>
-    <mergeCell ref="E91:F91"/>
-    <mergeCell ref="E92:F92"/>
-    <mergeCell ref="E105:F105"/>
-    <mergeCell ref="E106:F106"/>
-    <mergeCell ref="E107:F107"/>
-    <mergeCell ref="E109:F109"/>
-    <mergeCell ref="E110:F110"/>
-    <mergeCell ref="E93:F93"/>
-    <mergeCell ref="E94:F94"/>
-    <mergeCell ref="E95:F95"/>
-    <mergeCell ref="E96:F96"/>
-    <mergeCell ref="E97:F97"/>
-    <mergeCell ref="E98:F98"/>
-    <mergeCell ref="E99:F99"/>
-    <mergeCell ref="E100:F100"/>
-    <mergeCell ref="E101:F101"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="C183:D183"/>
-    <mergeCell ref="E183:F183"/>
-    <mergeCell ref="E120:F120"/>
-    <mergeCell ref="E121:F121"/>
-    <mergeCell ref="E122:F122"/>
-    <mergeCell ref="E123:F123"/>
-    <mergeCell ref="E124:F124"/>
-    <mergeCell ref="E125:F125"/>
-    <mergeCell ref="E126:F126"/>
-    <mergeCell ref="E127:F127"/>
-    <mergeCell ref="E128:F128"/>
-    <mergeCell ref="E111:F111"/>
-    <mergeCell ref="E112:F112"/>
-    <mergeCell ref="E113:F113"/>
-    <mergeCell ref="E114:F114"/>
-    <mergeCell ref="E115:F115"/>
-    <mergeCell ref="E116:F116"/>
-    <mergeCell ref="E117:F117"/>
-    <mergeCell ref="E118:F118"/>
-    <mergeCell ref="E119:F119"/>
-    <mergeCell ref="E102:F102"/>
-    <mergeCell ref="E103:F103"/>
-    <mergeCell ref="E104:F104"/>
-    <mergeCell ref="C189:D189"/>
-    <mergeCell ref="C190:D190"/>
-    <mergeCell ref="E184:F194"/>
-    <mergeCell ref="C184:D184"/>
-    <mergeCell ref="C185:D185"/>
-    <mergeCell ref="C186:D186"/>
-    <mergeCell ref="C187:D187"/>
-    <mergeCell ref="C188:D188"/>
-    <mergeCell ref="E129:F129"/>
-    <mergeCell ref="E130:F130"/>
-    <mergeCell ref="E131:F131"/>
-    <mergeCell ref="E132:F132"/>
-    <mergeCell ref="E133:F133"/>
-    <mergeCell ref="E134:F134"/>
-    <mergeCell ref="E135:F135"/>
-    <mergeCell ref="C134:D134"/>
-    <mergeCell ref="C135:D135"/>
-    <mergeCell ref="C130:D130"/>
-    <mergeCell ref="C131:D131"/>
-    <mergeCell ref="C132:D132"/>
-    <mergeCell ref="C133:D133"/>
-    <mergeCell ref="E165:F165"/>
-    <mergeCell ref="E166:F166"/>
-    <mergeCell ref="E167:F167"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="300" r:id="rId1"/>
